--- a/CPL_Initiative_Project_List_v3.xlsx
+++ b/CPL_Initiative_Project_List_v3.xlsx
@@ -1,16 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-150" yWindow="0" windowWidth="22320" windowHeight="17385" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project List" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Update Log" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20260324 CPL Budget" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FUND" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Positions" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Project List" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Update Log" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="20260324 CPL Budget" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="FUND" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Positions" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="KPI_Config" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="Comparison_Tool_Data_Full">#REF!</definedName>
@@ -34,7 +35,7 @@
     <numFmt numFmtId="167" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="168" formatCode="_([$$-409]* #,##0_);_([$$-409]* \(#,##0\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="46">
+  <fonts count="47">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -328,8 +329,13 @@
     <font>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="14">
+  <fills count="15">
     <fill>
       <patternFill/>
     </fill>
@@ -405,6 +411,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF8E7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000A2240"/>
+        <bgColor rgb="000A2240"/>
       </patternFill>
     </fill>
   </fills>
@@ -759,7 +771,7 @@
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="221">
+  <cellXfs count="222">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1392,6 +1404,9 @@
     <xf numFmtId="0" fontId="44" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1475,14 +1490,14 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1200" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
@@ -1505,8 +1520,8 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -1523,7 +1538,7 @@
             <v>Total Budget</v>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1531,10 +1546,10 @@
             <idx val="0"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:schemeClr val="accent1"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:ln w="19050">
                 <a:solidFill>
                   <a:schemeClr val="lt1"/>
                 </a:solidFill>
@@ -1546,10 +1561,10 @@
             <idx val="1"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:schemeClr val="accent2"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:ln w="19050">
                 <a:solidFill>
                   <a:schemeClr val="lt1"/>
                 </a:solidFill>
@@ -1561,10 +1576,10 @@
             <idx val="2"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:schemeClr val="accent3"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:ln w="19050">
                 <a:solidFill>
                   <a:schemeClr val="lt1"/>
                 </a:solidFill>
@@ -1576,10 +1591,10 @@
             <idx val="3"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:schemeClr val="accent4"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:ln w="19050">
                 <a:solidFill>
                   <a:schemeClr val="lt1"/>
                 </a:solidFill>
@@ -1591,10 +1606,10 @@
             <idx val="4"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:schemeClr val="accent5"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:ln w="19050">
                 <a:solidFill>
                   <a:schemeClr val="lt1"/>
                 </a:solidFill>
@@ -1606,10 +1621,10 @@
             <idx val="5"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:schemeClr val="accent6"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:ln w="19050">
                 <a:solidFill>
                   <a:schemeClr val="lt1"/>
                 </a:solidFill>
@@ -1621,12 +1636,12 @@
             <idx val="6"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:schemeClr val="accent1">
                   <a:lumMod val="60000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:ln w="19050">
                 <a:solidFill>
                   <a:schemeClr val="lt1"/>
                 </a:solidFill>
@@ -1638,12 +1653,12 @@
             <idx val="7"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:schemeClr val="accent2">
                   <a:lumMod val="60000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:ln w="19050">
                 <a:solidFill>
                   <a:schemeClr val="lt1"/>
                 </a:solidFill>
@@ -1653,18 +1668,18 @@
           </dPt>
           <dLbls>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -1771,16 +1786,16 @@
       <legendPos val="b"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr rtl="0">
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -1805,10 +1820,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -1823,14 +1838,14 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1200" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
@@ -1853,8 +1868,8 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -1871,7 +1886,7 @@
             <v>Total Budget</v>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1879,10 +1894,10 @@
             <idx val="0"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:schemeClr val="accent1"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:ln w="19050">
                 <a:solidFill>
                   <a:schemeClr val="lt1"/>
                 </a:solidFill>
@@ -1894,10 +1909,10 @@
             <idx val="1"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:schemeClr val="accent2"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:ln w="19050">
                 <a:solidFill>
                   <a:schemeClr val="lt1"/>
                 </a:solidFill>
@@ -1909,10 +1924,10 @@
             <idx val="2"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:schemeClr val="accent3"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:ln w="19050">
                 <a:solidFill>
                   <a:schemeClr val="lt1"/>
                 </a:solidFill>
@@ -1922,18 +1937,18 @@
           </dPt>
           <dLbls>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="1100" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -2010,16 +2025,16 @@
       <legendPos val="b"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr rtl="0">
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -2044,10 +2059,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -2102,7 +2117,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>1</col>
@@ -2122,9 +2137,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2149,9 +2164,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+          <c:chart r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2449,7 +2464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD52"/>
+  <dimension ref="A1:AG52"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="16" defaultRowHeight="15" outlineLevelRow="1"/>
   <cols>
     <col width="6" customWidth="1" style="187" min="1" max="1"/>
@@ -11287,38 +11302,14 @@
           <t>$6M P98 (CO)</t>
         </is>
       </c>
-      <c r="F6" s="21">
-        <f>SUMIF($E$19:$E$52,$E6,$F$19:$F$52)</f>
-        <v/>
-      </c>
-      <c r="G6" s="22">
-        <f>SUMIF($E$19:$E$52,$E6,G$19:G$52)</f>
-        <v/>
-      </c>
-      <c r="H6" s="21">
-        <f>SUMIF($E$19:$E$52,$E6,H$19:H$52)</f>
-        <v/>
-      </c>
-      <c r="I6" s="21">
-        <f>SUMIF($E$19:$E$52,$E6,I$19:I$52)</f>
-        <v/>
-      </c>
-      <c r="J6" s="21">
-        <f>SUMIF($E$19:$E$52,$E6,J$19:J$52)</f>
-        <v/>
-      </c>
-      <c r="K6" s="21">
-        <f>SUMIF($E$19:$E$52,$E6,K$19:K$52)</f>
-        <v/>
-      </c>
-      <c r="L6" s="23">
-        <f>SUM(F6+H6+I6+J6+K6,0)</f>
-        <v/>
-      </c>
-      <c r="M6" s="24">
-        <f>(F6+H6+I6+J6+K6)/5</f>
-        <v/>
-      </c>
+      <c r="F6" s="21" t="n"/>
+      <c r="G6" s="22" t="n"/>
+      <c r="H6" s="21" t="n"/>
+      <c r="I6" s="21" t="n"/>
+      <c r="J6" s="21" t="n"/>
+      <c r="K6" s="21" t="n"/>
+      <c r="L6" s="23" t="n"/>
+      <c r="M6" s="24" t="n"/>
     </row>
     <row r="7" outlineLevel="2" ht="25.5" customHeight="1">
       <c r="B7" s="20" t="inlineStr">
@@ -11337,38 +11328,14 @@
           <t>$6M P98 (RCCD)</t>
         </is>
       </c>
-      <c r="F7" s="21">
-        <f>SUMIF($E$19:$E$52,$E7,$F$19:$F$52)</f>
-        <v/>
-      </c>
-      <c r="G7" s="22">
-        <f>SUMIF($E$19:$E$52,$E7,$G$19:$G$52)</f>
-        <v/>
-      </c>
-      <c r="H7" s="21">
-        <f>SUMIF($E$19:$E$52,$E7,H$19:H$52)</f>
-        <v/>
-      </c>
-      <c r="I7" s="21">
-        <f>SUMIF($E$19:$E$52,$E7,I$19:I$52)</f>
-        <v/>
-      </c>
-      <c r="J7" s="21">
-        <f>SUMIF($E$19:$E$52,$E7,J$19:J$52)</f>
-        <v/>
-      </c>
-      <c r="K7" s="21">
-        <f>SUMIF($E$19:$E$52,$E7,K$19:K$52)</f>
-        <v/>
-      </c>
-      <c r="L7" s="23">
-        <f>SUM(F7+H7+I7+J7+K7,0)</f>
-        <v/>
-      </c>
-      <c r="M7" s="24">
-        <f>(F7+H7+I7+J7+K7)/5</f>
-        <v/>
-      </c>
+      <c r="F7" s="21" t="n"/>
+      <c r="G7" s="22" t="n"/>
+      <c r="H7" s="21" t="n"/>
+      <c r="I7" s="21" t="n"/>
+      <c r="J7" s="21" t="n"/>
+      <c r="K7" s="21" t="n"/>
+      <c r="L7" s="23" t="n"/>
+      <c r="M7" s="24" t="n"/>
     </row>
     <row r="8" outlineLevel="2" ht="25.5" customFormat="1" customHeight="1" s="28">
       <c r="A8" s="25" t="n"/>
@@ -11388,38 +11355,14 @@
           <t>$5M P98 Ongoing</t>
         </is>
       </c>
-      <c r="F8" s="21">
-        <f>SUMIF($E$19:$E$52,$E8,$F$19:$F$52)</f>
-        <v/>
-      </c>
-      <c r="G8" s="22">
-        <f>SUMIF($E$19:$E$52,$E8,$G$19:$G$52)</f>
-        <v/>
-      </c>
-      <c r="H8" s="21">
-        <f>SUMIF($E$19:$E$52,$E8,H$19:H$52)</f>
-        <v/>
-      </c>
-      <c r="I8" s="21">
-        <f>SUMIF($E$19:$E$52,$E8,I$19:I$52)</f>
-        <v/>
-      </c>
-      <c r="J8" s="21">
-        <f>SUMIF($E$19:$E$52,$E8,J$19:J$52)</f>
-        <v/>
-      </c>
-      <c r="K8" s="21">
-        <f>SUMIF($E$19:$E$52,$E8,K$19:K$52)</f>
-        <v/>
-      </c>
-      <c r="L8" s="23">
-        <f>SUM(F8+H8+I8+J8+K8,0)</f>
-        <v/>
-      </c>
-      <c r="M8" s="24">
-        <f>(F8+H8+I8+J8+K8)/5</f>
-        <v/>
-      </c>
+      <c r="F8" s="21" t="n"/>
+      <c r="G8" s="22" t="n"/>
+      <c r="H8" s="21" t="n"/>
+      <c r="I8" s="21" t="n"/>
+      <c r="J8" s="21" t="n"/>
+      <c r="K8" s="21" t="n"/>
+      <c r="L8" s="23" t="n"/>
+      <c r="M8" s="24" t="n"/>
     </row>
     <row r="9" outlineLevel="2" ht="25.5" customHeight="1">
       <c r="B9" s="20" t="inlineStr">
@@ -11438,38 +11381,14 @@
           <t>$15M P98</t>
         </is>
       </c>
-      <c r="F9" s="21">
-        <f>SUMIF($E$19:$E$52,$E9,$F$19:$F$52)</f>
-        <v/>
-      </c>
-      <c r="G9" s="22">
-        <f>SUMIF($E$19:$E$52,$E9,$G$19:$G$52)</f>
-        <v/>
-      </c>
-      <c r="H9" s="21">
-        <f>SUMIF($E$19:$E$52,$E9,H$19:H$52)</f>
-        <v/>
-      </c>
-      <c r="I9" s="21">
-        <f>SUMIF($E$19:$E$52,$E9,I$19:I$52)</f>
-        <v/>
-      </c>
-      <c r="J9" s="21">
-        <f>SUMIF($E$19:$E$52,$E9,J$19:J$52)</f>
-        <v/>
-      </c>
-      <c r="K9" s="21">
-        <f>SUMIF($E$19:$E$52,$E9,K$19:K$52)</f>
-        <v/>
-      </c>
-      <c r="L9" s="23">
-        <f>SUM(F9+H9+I9+J9+K9,0)</f>
-        <v/>
-      </c>
-      <c r="M9" s="24">
-        <f>(F9+H9+I9+J9+K9)/5</f>
-        <v/>
-      </c>
+      <c r="F9" s="21" t="n"/>
+      <c r="G9" s="22" t="n"/>
+      <c r="H9" s="21" t="n"/>
+      <c r="I9" s="21" t="n"/>
+      <c r="J9" s="21" t="n"/>
+      <c r="K9" s="21" t="n"/>
+      <c r="L9" s="23" t="n"/>
+      <c r="M9" s="24" t="n"/>
     </row>
     <row r="10" outlineLevel="2" ht="25.5" customHeight="1">
       <c r="B10" s="30" t="inlineStr">
@@ -11488,14 +11407,8 @@
           <t>$2M P98</t>
         </is>
       </c>
-      <c r="F10" s="31">
-        <f>SUMIF($E$19:$E$52,$E10,$F$19:$F$52)</f>
-        <v/>
-      </c>
-      <c r="G10" s="32">
-        <f>SUMIF($E$19:$E$52,$E10,$G$19:$G$52)</f>
-        <v/>
-      </c>
+      <c r="F10" s="31" t="n"/>
+      <c r="G10" s="32" t="n"/>
       <c r="H10" s="33" t="n">
         <v>2000000</v>
       </c>
@@ -11508,14 +11421,8 @@
       <c r="K10" s="33" t="n">
         <v>2000000</v>
       </c>
-      <c r="L10" s="34">
-        <f>SUM(F10+H10+I10+J10+K10,0)</f>
-        <v/>
-      </c>
-      <c r="M10" s="35">
-        <f>(F10+H10+I10+J10+K10)/5</f>
-        <v/>
-      </c>
+      <c r="L10" s="34" t="n"/>
+      <c r="M10" s="35" t="n"/>
     </row>
     <row r="11" outlineLevel="2" ht="25.5" customHeight="1">
       <c r="B11" s="30" t="inlineStr">
@@ -11534,14 +11441,8 @@
           <t>$35M P98</t>
         </is>
       </c>
-      <c r="F11" s="31">
-        <f>SUMIF($E$19:$E$52,$E11,$F$19:$F$52)</f>
-        <v/>
-      </c>
-      <c r="G11" s="32">
-        <f>SUMIF($E$19:$E$52,$E11,$G$19:$G$52)</f>
-        <v/>
-      </c>
+      <c r="F11" s="31" t="n"/>
+      <c r="G11" s="32" t="n"/>
       <c r="H11" s="33" t="n">
         <v>15000000</v>
       </c>
@@ -11554,14 +11455,8 @@
       <c r="K11" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="L11" s="34">
-        <f>SUM(F11+H11+I11+J11+K11,0)</f>
-        <v/>
-      </c>
-      <c r="M11" s="35">
-        <f>(F11+H11+I11+J11+K11)/5</f>
-        <v/>
-      </c>
+      <c r="L11" s="34" t="n"/>
+      <c r="M11" s="35" t="n"/>
     </row>
     <row r="12" outlineLevel="1">
       <c r="B12" s="36" t="inlineStr">
@@ -11580,38 +11475,14 @@
           <t>ALL</t>
         </is>
       </c>
-      <c r="F12" s="38">
-        <f>SUMIF($D$19:$D$52,$B12,$F$19:$F$52)</f>
-        <v/>
-      </c>
-      <c r="G12" s="38">
-        <f>SUMIF($D$19:$D$52,$B12,G$19:G$52)</f>
-        <v/>
-      </c>
-      <c r="H12" s="38">
-        <f>SUMIF($D$19:$D$52,$B12,H$19:H$52)</f>
-        <v/>
-      </c>
-      <c r="I12" s="38">
-        <f>SUMIF($D$19:$D$52,$B12,I$19:I$52)</f>
-        <v/>
-      </c>
-      <c r="J12" s="38">
-        <f>SUMIF($D$19:$D$52,$B12,J$19:J$52)</f>
-        <v/>
-      </c>
-      <c r="K12" s="38">
-        <f>SUMIF($D$19:$D$52,$B12,K$19:K$52)</f>
-        <v/>
-      </c>
-      <c r="L12" s="38">
-        <f>L19+L20+L21+L23+L26+L29+L34+L39+L40+L42+L46+L47+L48+L49+L50+L51</f>
-        <v/>
-      </c>
-      <c r="M12" s="39">
-        <f>(F12+H12+I12+J12+K12)/5</f>
-        <v/>
-      </c>
+      <c r="F12" s="38" t="n"/>
+      <c r="G12" s="38" t="n"/>
+      <c r="H12" s="38" t="n"/>
+      <c r="I12" s="38" t="n"/>
+      <c r="J12" s="38" t="n"/>
+      <c r="K12" s="38" t="n"/>
+      <c r="L12" s="38" t="n"/>
+      <c r="M12" s="39" t="n"/>
     </row>
     <row r="13" outlineLevel="1">
       <c r="B13" s="36" t="inlineStr">
@@ -11630,38 +11501,14 @@
           <t>ALL</t>
         </is>
       </c>
-      <c r="F13" s="38">
-        <f>SUMIF($D$19:$D$52,$B13,$F$19:$F$52)</f>
-        <v/>
-      </c>
-      <c r="G13" s="38">
-        <f>SUMIF($D$19:$D$52,$B13,G$19:G$52)</f>
-        <v/>
-      </c>
-      <c r="H13" s="38">
-        <f>SUMIF($D$19:$D$52,$B13,H$19:H$52)</f>
-        <v/>
-      </c>
-      <c r="I13" s="38">
-        <f>SUMIF($D$19:$D$52,$B13,I$19:I$52)</f>
-        <v/>
-      </c>
-      <c r="J13" s="38">
-        <f>SUMIF($D$19:$D$52,$B13,J$19:J$52)</f>
-        <v/>
-      </c>
-      <c r="K13" s="38">
-        <f>SUMIF($D$19:$D$52,$B13,K$19:K$52)</f>
-        <v/>
-      </c>
-      <c r="L13" s="38">
-        <f>SUM(L23+L32+L33+L36+L43+L45+L37)</f>
-        <v/>
-      </c>
-      <c r="M13" s="39">
-        <f>(F13+H13+I13+J13+K13)/5</f>
-        <v/>
-      </c>
+      <c r="F13" s="38" t="n"/>
+      <c r="G13" s="38" t="n"/>
+      <c r="H13" s="38" t="n"/>
+      <c r="I13" s="38" t="n"/>
+      <c r="J13" s="38" t="n"/>
+      <c r="K13" s="38" t="n"/>
+      <c r="L13" s="38" t="n"/>
+      <c r="M13" s="39" t="n"/>
     </row>
     <row r="14" outlineLevel="1">
       <c r="B14" s="36" t="inlineStr">
@@ -11680,38 +11527,14 @@
           <t>ALL</t>
         </is>
       </c>
-      <c r="F14" s="38">
-        <f>SUMIF($D$19:$D$52,$B14,$F$19:$F$52)</f>
-        <v/>
-      </c>
-      <c r="G14" s="38">
-        <f>SUMIF($D$19:$D$52,$B14,G$19:G$52)</f>
-        <v/>
-      </c>
-      <c r="H14" s="38">
-        <f>SUMIF($D$19:$D$52,$B14,H$19:H$52)</f>
-        <v/>
-      </c>
-      <c r="I14" s="38">
-        <f>SUMIF($D$19:$D$52,$B14,I$19:I$52)</f>
-        <v/>
-      </c>
-      <c r="J14" s="38">
-        <f>SUMIF($D$19:$D$52,$B14,J$19:J$52)</f>
-        <v/>
-      </c>
-      <c r="K14" s="38">
-        <f>SUMIF($D$19:$D$52,$B14,K$19:K$52)</f>
-        <v/>
-      </c>
-      <c r="L14" s="38">
-        <f>L41</f>
-        <v/>
-      </c>
-      <c r="M14" s="39">
-        <f>(F14+H14+I14+J14+K14)/5</f>
-        <v/>
-      </c>
+      <c r="F14" s="38" t="n"/>
+      <c r="G14" s="38" t="n"/>
+      <c r="H14" s="38" t="n"/>
+      <c r="I14" s="38" t="n"/>
+      <c r="J14" s="38" t="n"/>
+      <c r="K14" s="38" t="n"/>
+      <c r="L14" s="38" t="n"/>
+      <c r="M14" s="39" t="n"/>
     </row>
     <row r="15" outlineLevel="1">
       <c r="B15" s="40" t="inlineStr">
@@ -11730,38 +11553,14 @@
           <t>ALL</t>
         </is>
       </c>
-      <c r="F15" s="38">
-        <f>SUM(F12:F14)</f>
-        <v/>
-      </c>
-      <c r="G15" s="38">
-        <f>SUM(G12:G14)</f>
-        <v/>
-      </c>
-      <c r="H15" s="38">
-        <f>SUM(H12:H14)</f>
-        <v/>
-      </c>
-      <c r="I15" s="38">
-        <f>SUM(I12:I14)</f>
-        <v/>
-      </c>
-      <c r="J15" s="38">
-        <f>SUM(J12:J14)</f>
-        <v/>
-      </c>
-      <c r="K15" s="38">
-        <f>SUM(K12:K14)</f>
-        <v/>
-      </c>
-      <c r="L15" s="38">
-        <f>SUM(L12:L14)</f>
-        <v/>
-      </c>
-      <c r="M15" s="39">
-        <f>(F15+H15+I15+J15+K15)/5</f>
-        <v/>
-      </c>
+      <c r="F15" s="38" t="n"/>
+      <c r="G15" s="38" t="n"/>
+      <c r="H15" s="38" t="n"/>
+      <c r="I15" s="38" t="n"/>
+      <c r="J15" s="38" t="n"/>
+      <c r="K15" s="38" t="n"/>
+      <c r="L15" s="38" t="n"/>
+      <c r="M15" s="39" t="n"/>
     </row>
     <row r="16" outlineLevel="1">
       <c r="B16" s="41" t="inlineStr">
@@ -11772,10 +11571,7 @@
       <c r="C16" s="42" t="n"/>
       <c r="D16" s="42" t="n"/>
       <c r="E16" s="42" t="n"/>
-      <c r="F16" s="43">
-        <f>15000000-F9</f>
-        <v/>
-      </c>
+      <c r="F16" s="43" t="n"/>
       <c r="G16" s="38" t="n"/>
       <c r="H16" s="38" t="n"/>
       <c r="I16" s="38" t="n"/>
@@ -11840,37 +11636,16 @@
           <t>$5M P98 Ongoing</t>
         </is>
       </c>
-      <c r="F19" s="48">
-        <f>F76-145200</f>
-        <v/>
-      </c>
+      <c r="F19" s="48" t="n"/>
       <c r="G19" s="49" t="n">
         <v>1230000</v>
       </c>
-      <c r="H19" s="48">
-        <f>H76+H77</f>
-        <v/>
-      </c>
-      <c r="I19" s="48">
-        <f>I76+I77</f>
-        <v/>
-      </c>
-      <c r="J19" s="48">
-        <f>J76+J77</f>
-        <v/>
-      </c>
-      <c r="K19" s="48">
-        <f>K76+K77</f>
-        <v/>
-      </c>
-      <c r="L19" s="50">
-        <f>SUM(F19+H19+I19+J19+K19)</f>
-        <v/>
-      </c>
-      <c r="M19" s="24">
-        <f>(F19+H19+I19+J19+K19)/5</f>
-        <v/>
-      </c>
+      <c r="H19" s="48" t="n"/>
+      <c r="I19" s="48" t="n"/>
+      <c r="J19" s="48" t="n"/>
+      <c r="K19" s="48" t="n"/>
+      <c r="L19" s="50" t="n"/>
+      <c r="M19" s="24" t="n"/>
     </row>
     <row r="20" outlineLevel="3" ht="113.25" customHeight="1">
       <c r="B20" s="200" t="n"/>
@@ -11889,10 +11664,7 @@
           <t>$6M P98 (RCCD)</t>
         </is>
       </c>
-      <c r="F20" s="48">
-        <f>F77+145200</f>
-        <v/>
-      </c>
+      <c r="F20" s="48" t="n"/>
       <c r="G20" s="49" t="n">
         <v>1300000</v>
       </c>
@@ -11908,14 +11680,8 @@
       <c r="K20" s="48" t="n">
         <v>0</v>
       </c>
-      <c r="L20" s="50">
-        <f>SUM(F20+H20+I20+J20+K20)</f>
-        <v/>
-      </c>
-      <c r="M20" s="24">
-        <f>(F20+H20+I20+J20+K20)/5</f>
-        <v/>
-      </c>
+      <c r="L20" s="50" t="n"/>
+      <c r="M20" s="24" t="n"/>
     </row>
     <row r="21" ht="66.75" customHeight="1">
       <c r="B21" s="199" t="inlineStr">
@@ -11940,10 +11706,7 @@
           <t>$6M P98 (RCCD)</t>
         </is>
       </c>
-      <c r="F21" s="51">
-        <f>396560</f>
-        <v/>
-      </c>
+      <c r="F21" s="51" t="n"/>
       <c r="G21" s="49" t="n">
         <v>0</v>
       </c>
@@ -11959,14 +11722,8 @@
       <c r="K21" s="48" t="n">
         <v>0</v>
       </c>
-      <c r="L21" s="50">
-        <f>SUM(F21+H21+I21+J21+K21)</f>
-        <v/>
-      </c>
-      <c r="M21" s="24">
-        <f>(F21+H21+I21+J21+K21)/5</f>
-        <v/>
-      </c>
+      <c r="L21" s="50" t="n"/>
+      <c r="M21" s="24" t="n"/>
     </row>
     <row r="22" ht="72" customHeight="1">
       <c r="B22" s="200" t="n"/>
@@ -12003,14 +11760,8 @@
       <c r="K22" s="48" t="n">
         <v>100000</v>
       </c>
-      <c r="L22" s="50">
-        <f>SUM(F22+H22+I22+J22+K22)</f>
-        <v/>
-      </c>
-      <c r="M22" s="24">
-        <f>(F22+H22+I22+J22+K22)/5</f>
-        <v/>
-      </c>
+      <c r="L22" s="50" t="n"/>
+      <c r="M22" s="24" t="n"/>
     </row>
     <row r="23" ht="78.75" customHeight="1">
       <c r="B23" s="199" t="inlineStr">
@@ -12052,14 +11803,8 @@
       <c r="K23" s="52" t="n">
         <v>0</v>
       </c>
-      <c r="L23" s="50">
-        <f>SUM(F23+H23+I23+J23+K23)</f>
-        <v/>
-      </c>
-      <c r="M23" s="24">
-        <f>(F23+H23+I23+J23+K23)/5</f>
-        <v/>
-      </c>
+      <c r="L23" s="50" t="n"/>
+      <c r="M23" s="24" t="n"/>
     </row>
     <row r="24" ht="51" customHeight="1">
       <c r="B24" s="196" t="n"/>
@@ -12096,14 +11841,8 @@
       <c r="K24" s="48" t="n">
         <v>0</v>
       </c>
-      <c r="L24" s="50">
-        <f>SUM(F24+H24+I24+J24+K24)</f>
-        <v/>
-      </c>
-      <c r="M24" s="24">
-        <f>(F24+H24+I24+J24+K24)/5</f>
-        <v/>
-      </c>
+      <c r="L24" s="50" t="n"/>
+      <c r="M24" s="24" t="n"/>
     </row>
     <row r="25" ht="51" customHeight="1">
       <c r="B25" s="200" t="n"/>
@@ -12140,14 +11879,8 @@
       <c r="K25" s="48" t="n">
         <v>100000</v>
       </c>
-      <c r="L25" s="50">
-        <f>SUM(F25+H25+I25+J25+K25)</f>
-        <v/>
-      </c>
-      <c r="M25" s="24">
-        <f>(F25+H25+I25+J25+K25)/5</f>
-        <v/>
-      </c>
+      <c r="L25" s="50" t="n"/>
+      <c r="M25" s="24" t="n"/>
     </row>
     <row r="26" ht="25.5" customHeight="1">
       <c r="B26" s="199" t="inlineStr">
@@ -12189,14 +11922,8 @@
       <c r="K26" s="48" t="n">
         <v>0</v>
       </c>
-      <c r="L26" s="50">
-        <f>SUM(F26+H26+I26+J26+K26)</f>
-        <v/>
-      </c>
-      <c r="M26" s="24">
-        <f>(F26+H26+I26+J26+K26)/5</f>
-        <v/>
-      </c>
+      <c r="L26" s="50" t="n"/>
+      <c r="M26" s="24" t="n"/>
     </row>
     <row r="27" ht="25.5" customHeight="1">
       <c r="B27" s="196" t="n"/>
@@ -12233,14 +11960,8 @@
       <c r="K27" s="48" t="n">
         <v>0</v>
       </c>
-      <c r="L27" s="50">
-        <f>SUM(F27+H27+I27+J27+K27)</f>
-        <v/>
-      </c>
-      <c r="M27" s="24">
-        <f>(F27+H27+I27+J27+K27)/5</f>
-        <v/>
-      </c>
+      <c r="L27" s="50" t="n"/>
+      <c r="M27" s="24" t="n"/>
     </row>
     <row r="28" ht="25.5" customHeight="1">
       <c r="B28" s="200" t="n"/>
@@ -12277,14 +11998,8 @@
       <c r="K28" s="48" t="n">
         <v>50000</v>
       </c>
-      <c r="L28" s="50">
-        <f>SUM(F28+H28+I28+J28+K28)</f>
-        <v/>
-      </c>
-      <c r="M28" s="24">
-        <f>(F28+H28+I28+J28+K28)/5</f>
-        <v/>
-      </c>
+      <c r="L28" s="50" t="n"/>
+      <c r="M28" s="24" t="n"/>
     </row>
     <row r="29" outlineLevel="1" ht="51" customHeight="1">
       <c r="B29" s="195" t="inlineStr">
@@ -12310,10 +12025,7 @@
           <t>$6M P98 (RCCD)</t>
         </is>
       </c>
-      <c r="F29" s="48">
-        <f>50000+69000</f>
-        <v/>
-      </c>
+      <c r="F29" s="48" t="n"/>
       <c r="G29" s="49" t="n">
         <v>119000</v>
       </c>
@@ -12329,14 +12041,8 @@
       <c r="K29" s="48" t="n">
         <v>0</v>
       </c>
-      <c r="L29" s="50">
-        <f>SUM(F29+H29+I29+J29+K29)</f>
-        <v/>
-      </c>
-      <c r="M29" s="24">
-        <f>(F29+H29+I29+J29+K29)/5</f>
-        <v/>
-      </c>
+      <c r="L29" s="50" t="n"/>
+      <c r="M29" s="24" t="n"/>
     </row>
     <row r="30" outlineLevel="1" ht="51" customHeight="1">
       <c r="B30" s="196" t="n"/>
@@ -12373,14 +12079,8 @@
       <c r="K30" s="48" t="n">
         <v>100000</v>
       </c>
-      <c r="L30" s="50">
-        <f>SUM(F30+H30+I30+J30+K30)</f>
-        <v/>
-      </c>
-      <c r="M30" s="24">
-        <f>(F30+H30+I30+J30+K30)/5</f>
-        <v/>
-      </c>
+      <c r="L30" s="50" t="n"/>
+      <c r="M30" s="24" t="n"/>
     </row>
     <row r="31" outlineLevel="1" ht="51" customHeight="1">
       <c r="B31" s="197" t="n"/>
@@ -12417,14 +12117,8 @@
       <c r="K31" s="48" t="n">
         <v>0</v>
       </c>
-      <c r="L31" s="50">
-        <f>SUM(F31+H31+I31+J31+K31)</f>
-        <v/>
-      </c>
-      <c r="M31" s="24">
-        <f>(F31+H31+I31+J31+K31)/5</f>
-        <v/>
-      </c>
+      <c r="L31" s="50" t="n"/>
+      <c r="M31" s="24" t="n"/>
     </row>
     <row r="32" ht="76.5" customHeight="1">
       <c r="B32" s="53" t="inlineStr">
@@ -12448,10 +12142,7 @@
           <t>$6M P98 (CO)</t>
         </is>
       </c>
-      <c r="F32" s="48">
-        <f>1563900</f>
-        <v/>
-      </c>
+      <c r="F32" s="48" t="n"/>
       <c r="G32" s="49" t="n">
         <v>1563900</v>
       </c>
@@ -12467,14 +12158,8 @@
       <c r="K32" s="48" t="n">
         <v>0</v>
       </c>
-      <c r="L32" s="50">
-        <f>SUM(F32+H32+I32+J32+K32)</f>
-        <v/>
-      </c>
-      <c r="M32" s="24">
-        <f>(F32+H32+I32+J32+K32)/5</f>
-        <v/>
-      </c>
+      <c r="L32" s="50" t="n"/>
+      <c r="M32" s="24" t="n"/>
     </row>
     <row r="33" ht="51" customHeight="1">
       <c r="B33" s="53" t="inlineStr">
@@ -12516,14 +12201,8 @@
       <c r="K33" s="48" t="n">
         <v>0</v>
       </c>
-      <c r="L33" s="50">
-        <f>SUM(F33+H33+I33+J33+K33)</f>
-        <v/>
-      </c>
-      <c r="M33" s="24">
-        <f>(F33+H33+I33+J33+K33)/5</f>
-        <v/>
-      </c>
+      <c r="L33" s="50" t="n"/>
+      <c r="M33" s="24" t="n"/>
     </row>
     <row r="34" ht="53.25" customHeight="1">
       <c r="B34" s="204" t="inlineStr">
@@ -12565,14 +12244,8 @@
       <c r="K34" s="48" t="n">
         <v>0</v>
       </c>
-      <c r="L34" s="50">
-        <f>SUM(F34+H34+I34+J34+K34)</f>
-        <v/>
-      </c>
-      <c r="M34" s="24">
-        <f>(F34+H34+I34+J34+K34)/5</f>
-        <v/>
-      </c>
+      <c r="L34" s="50" t="n"/>
+      <c r="M34" s="24" t="n"/>
     </row>
     <row r="35" ht="53.25" customHeight="1">
       <c r="B35" s="205" t="n"/>
@@ -12609,14 +12282,8 @@
       <c r="K35" s="48" t="n">
         <v>0</v>
       </c>
-      <c r="L35" s="50">
-        <f>SUM(F35+H35+I35+J35+K35)</f>
-        <v/>
-      </c>
-      <c r="M35" s="24">
-        <f>(F35+H35+I35+J35+K35)/5</f>
-        <v/>
-      </c>
+      <c r="L35" s="50" t="n"/>
+      <c r="M35" s="24" t="n"/>
     </row>
     <row r="36" ht="63.75" customHeight="1">
       <c r="B36" s="53" t="inlineStr">
@@ -12658,14 +12325,8 @@
       <c r="K36" s="48" t="n">
         <v>0</v>
       </c>
-      <c r="L36" s="50">
-        <f>SUM(F36+H36+I36+J36+K36)</f>
-        <v/>
-      </c>
-      <c r="M36" s="24">
-        <f>(F36+H36+I36+J36+K36)/5</f>
-        <v/>
-      </c>
+      <c r="L36" s="50" t="n"/>
+      <c r="M36" s="24" t="n"/>
     </row>
     <row r="37" ht="42.75" customHeight="1">
       <c r="B37" s="204" t="inlineStr">
@@ -12707,14 +12368,8 @@
       <c r="K37" s="48" t="n">
         <v>0</v>
       </c>
-      <c r="L37" s="50">
-        <f>SUM(F37+H37+I37+J37+K37)</f>
-        <v/>
-      </c>
-      <c r="M37" s="24">
-        <f>(F37+H37+I37+J37+K37)/5</f>
-        <v/>
-      </c>
+      <c r="L37" s="50" t="n"/>
+      <c r="M37" s="24" t="n"/>
     </row>
     <row r="38" ht="52.5" customHeight="1">
       <c r="B38" s="205" t="n"/>
@@ -12751,14 +12406,8 @@
       <c r="K38" s="48" t="n">
         <v>0</v>
       </c>
-      <c r="L38" s="50">
-        <f>SUM(F38+H38+I38+J38+K38)</f>
-        <v/>
-      </c>
-      <c r="M38" s="24">
-        <f>(F38+H38+I38+J38+K38)/5</f>
-        <v/>
-      </c>
+      <c r="L38" s="50" t="n"/>
+      <c r="M38" s="24" t="n"/>
     </row>
     <row r="39" ht="63.75" customHeight="1">
       <c r="B39" s="199" t="inlineStr">
@@ -12788,28 +12437,16 @@
       <c r="G39" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="H39" s="48">
-        <f>25000+4000+40000-3275</f>
-        <v/>
-      </c>
-      <c r="I39" s="48">
-        <f>25000+4000+40000</f>
-        <v/>
-      </c>
+      <c r="H39" s="48" t="n"/>
+      <c r="I39" s="48" t="n"/>
       <c r="J39" s="48" t="n">
         <v>44000</v>
       </c>
       <c r="K39" s="48" t="n">
         <v>44000</v>
       </c>
-      <c r="L39" s="50">
-        <f>SUM(F39+H39+I39+J39+K39)</f>
-        <v/>
-      </c>
-      <c r="M39" s="24">
-        <f>(F39+H39+I39+J39+K39)/5</f>
-        <v/>
-      </c>
+      <c r="L39" s="50" t="n"/>
+      <c r="M39" s="24" t="n"/>
     </row>
     <row r="40" ht="63.75" customHeight="1">
       <c r="B40" s="199" t="inlineStr">
@@ -12851,14 +12488,8 @@
       <c r="K40" s="48" t="n">
         <v>15000</v>
       </c>
-      <c r="L40" s="50">
-        <f>SUM(F40+H40+I40+J40+K40)</f>
-        <v/>
-      </c>
-      <c r="M40" s="24">
-        <f>(F40+H40+I40+J40+K40)/5</f>
-        <v/>
-      </c>
+      <c r="L40" s="50" t="n"/>
+      <c r="M40" s="24" t="n"/>
     </row>
     <row r="41" ht="42" customHeight="1">
       <c r="B41" s="55" t="inlineStr">
@@ -12881,10 +12512,7 @@
           <t>$15M P98</t>
         </is>
       </c>
-      <c r="F41" s="48">
-        <f>118*50000</f>
-        <v/>
-      </c>
+      <c r="F41" s="48" t="n"/>
       <c r="G41" s="49" t="n">
         <v>5900000</v>
       </c>
@@ -12900,14 +12528,8 @@
       <c r="K41" s="48" t="n">
         <v>0</v>
       </c>
-      <c r="L41" s="50">
-        <f>SUM(F41+H41+I41+J41+K41)</f>
-        <v/>
-      </c>
-      <c r="M41" s="24">
-        <f>(F41+H41+I41+J41+K41)/5</f>
-        <v/>
-      </c>
+      <c r="L41" s="50" t="n"/>
+      <c r="M41" s="24" t="n"/>
     </row>
     <row r="42" ht="59.25" customHeight="1">
       <c r="B42" s="195" t="inlineStr">
@@ -12949,14 +12571,8 @@
       <c r="K42" s="48" t="n">
         <v>50000</v>
       </c>
-      <c r="L42" s="50">
-        <f>SUM(F42+H42+I42+J42+K42)</f>
-        <v/>
-      </c>
-      <c r="M42" s="24">
-        <f>(F42+H42+I42+J42+K42)/5</f>
-        <v/>
-      </c>
+      <c r="L42" s="50" t="n"/>
+      <c r="M42" s="24" t="n"/>
     </row>
     <row r="43" ht="69.75" customHeight="1">
       <c r="B43" s="196" t="n"/>
@@ -12974,10 +12590,7 @@
       <c r="F43" s="48" t="n">
         <v>233589</v>
       </c>
-      <c r="G43" s="49">
-        <f>340000-G42</f>
-        <v/>
-      </c>
+      <c r="G43" s="49" t="n"/>
       <c r="H43" s="48" t="n">
         <v>0</v>
       </c>
@@ -12990,14 +12603,8 @@
       <c r="K43" s="48" t="n">
         <v>0</v>
       </c>
-      <c r="L43" s="50">
-        <f>SUM(F43+H43+I43+J43+K43)</f>
-        <v/>
-      </c>
-      <c r="M43" s="24">
-        <f>(F43+H43+I43+J43+K43)/5</f>
-        <v/>
-      </c>
+      <c r="L43" s="50" t="n"/>
+      <c r="M43" s="24" t="n"/>
     </row>
     <row r="44" ht="69.75" customHeight="1">
       <c r="B44" s="197" t="n"/>
@@ -13034,14 +12641,8 @@
       <c r="K44" s="48" t="n">
         <v>200000</v>
       </c>
-      <c r="L44" s="50">
-        <f>SUM(F44+H44+I44+J44+K44)</f>
-        <v/>
-      </c>
-      <c r="M44" s="24">
-        <f>(F44+H44+I44+J44+K44)/5</f>
-        <v/>
-      </c>
+      <c r="L44" s="50" t="n"/>
+      <c r="M44" s="24" t="n"/>
     </row>
     <row r="45" ht="89.25" customHeight="1">
       <c r="B45" s="53" t="inlineStr">
@@ -13083,14 +12684,8 @@
       <c r="K45" s="48" t="n">
         <v>0</v>
       </c>
-      <c r="L45" s="50">
-        <f>SUM(F45+H45+I45+J45+K45)</f>
-        <v/>
-      </c>
-      <c r="M45" s="24">
-        <f>(F45+H45+I45+J45+K45)/5</f>
-        <v/>
-      </c>
+      <c r="L45" s="50" t="n"/>
+      <c r="M45" s="24" t="n"/>
     </row>
     <row r="46" ht="81" customHeight="1">
       <c r="B46" s="199" t="inlineStr">
@@ -13132,14 +12727,8 @@
       <c r="K46" s="48" t="n">
         <v>50000</v>
       </c>
-      <c r="L46" s="50">
-        <f>SUM(F46+H46+I46+J46+K46)</f>
-        <v/>
-      </c>
-      <c r="M46" s="24">
-        <f>(F46+H46+I46+J46+K46)/5</f>
-        <v/>
-      </c>
+      <c r="L46" s="50" t="n"/>
+      <c r="M46" s="24" t="n"/>
     </row>
     <row r="47" ht="38.25" customHeight="1">
       <c r="B47" s="199" t="inlineStr">
@@ -13163,38 +12752,14 @@
           <t>$5M P98 Ongoing</t>
         </is>
       </c>
-      <c r="F47" s="48">
-        <f>F103</f>
-        <v/>
-      </c>
-      <c r="G47" s="49">
-        <f>G103</f>
-        <v/>
-      </c>
-      <c r="H47" s="48">
-        <f>H103-H48</f>
-        <v/>
-      </c>
-      <c r="I47" s="48">
-        <f>I103-I48</f>
-        <v/>
-      </c>
-      <c r="J47" s="48">
-        <f>J103-J48</f>
-        <v/>
-      </c>
-      <c r="K47" s="48">
-        <f>K103-K48</f>
-        <v/>
-      </c>
-      <c r="L47" s="50">
-        <f>SUM(F47+H47+I47+J47+K47)</f>
-        <v/>
-      </c>
-      <c r="M47" s="24">
-        <f>(F47+H47+I47+J47+K47)/5</f>
-        <v/>
-      </c>
+      <c r="F47" s="48" t="n"/>
+      <c r="G47" s="49" t="n"/>
+      <c r="H47" s="48" t="n"/>
+      <c r="I47" s="48" t="n"/>
+      <c r="J47" s="48" t="n"/>
+      <c r="K47" s="48" t="n"/>
+      <c r="L47" s="50" t="n"/>
+      <c r="M47" s="24" t="n"/>
     </row>
     <row r="48" ht="87.75" customHeight="1">
       <c r="B48" s="200" t="n"/>
@@ -13231,19 +12796,13 @@
       <c r="K48" s="48" t="n">
         <v>1459794</v>
       </c>
-      <c r="L48" s="50">
-        <f>SUM(F48+H48+I48+J48+K48)</f>
-        <v/>
-      </c>
-      <c r="M48" s="24">
-        <f>(F48+H48+I48+J48+K48)/5</f>
-        <v/>
-      </c>
+      <c r="L48" s="50" t="n"/>
+      <c r="M48" s="24" t="n"/>
     </row>
     <row r="49" ht="51" customHeight="1">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t> </t>
         </is>
       </c>
       <c r="B49" s="199" t="inlineStr">
@@ -13285,14 +12844,8 @@
       <c r="K49" s="48" t="n">
         <v>30000</v>
       </c>
-      <c r="L49" s="50">
-        <f>SUM(F49+H49+I49+J49+K49)</f>
-        <v/>
-      </c>
-      <c r="M49" s="24">
-        <f>(F49+H49+I49+J49+K49)/5</f>
-        <v/>
-      </c>
+      <c r="L49" s="50" t="n"/>
+      <c r="M49" s="24" t="n"/>
     </row>
     <row r="50" ht="28.5" customHeight="1">
       <c r="B50" s="199" t="inlineStr">
@@ -13316,38 +12869,14 @@
           <t>$6M P98 (RCCD)</t>
         </is>
       </c>
-      <c r="F50" s="48">
-        <f>(SUMIFS(F$19:F$49,$E$19:$E$49,$E50,$D$19:$D$49,"Operations &amp; Support")+SUMIFS(F$19:F$49,$E$19:$E$49,$E50,$D$19:$D$49,"Special Projects"))*$F$81</f>
-        <v/>
-      </c>
-      <c r="G50" s="49">
-        <f>(SUMIFS(G$19:G$49,$E$19:$E$49,$E50,$D$19:$D$49,"Operations &amp; Support")+SUMIFS(G$19:G$49,$E$19:$E$49,$E50,$D$19:$D$49,"Special Projects"))*$F$81</f>
-        <v/>
-      </c>
-      <c r="H50" s="48">
-        <f>(SUMIFS(H$19:H$49,$E$19:$E$49,$E50,$D$19:$D$49,"Operations &amp; Support")+SUMIFS(H$19:H$49,$E$19:$E$49,$E50,$D$19:$D$49,"Special Projects"))*$F$81</f>
-        <v/>
-      </c>
-      <c r="I50" s="48">
-        <f>(SUMIFS(I$19:I$49,$E$19:$E$49,$E50,$D$19:$D$49,"Operations &amp; Support")+SUMIFS(I$19:I$49,$E$19:$E$49,$E50,$D$19:$D$49,"Special Projects"))*$F$81</f>
-        <v/>
-      </c>
-      <c r="J50" s="48">
-        <f>(SUMIFS(J$19:J$49,$E$19:$E$49,$E50,$D$19:$D$49,"Operations &amp; Support")+SUMIFS(J$19:J$49,$E$19:$E$49,$E50,$D$19:$D$49,"Special Projects"))*$F$81</f>
-        <v/>
-      </c>
-      <c r="K50" s="48">
-        <f>(SUMIFS(K$19:K$49,$E$19:$E$49,$E50,$D$19:$D$49,"Operations &amp; Support")+SUMIFS(K$19:K$49,$E$19:$E$49,$E50,$D$19:$D$49,"Special Projects"))*$F$81</f>
-        <v/>
-      </c>
-      <c r="L50" s="50">
-        <f>SUM(F50+H50+I50+J50+K50)</f>
-        <v/>
-      </c>
-      <c r="M50" s="24">
-        <f>(F50+H50+I50+J50+K50)/5</f>
-        <v/>
-      </c>
+      <c r="F50" s="48" t="n"/>
+      <c r="G50" s="49" t="n"/>
+      <c r="H50" s="48" t="n"/>
+      <c r="I50" s="48" t="n"/>
+      <c r="J50" s="48" t="n"/>
+      <c r="K50" s="48" t="n"/>
+      <c r="L50" s="50" t="n"/>
+      <c r="M50" s="24" t="n"/>
     </row>
     <row r="51" ht="27" customHeight="1">
       <c r="B51" s="196" t="n"/>
@@ -13366,38 +12895,14 @@
           <t>$5M P98 Ongoing</t>
         </is>
       </c>
-      <c r="F51" s="48">
-        <f>(SUMIFS(F$19:F$49,$E$19:$E$49,$E51,$D$19:$D$49,"Operations &amp; Support")+SUMIFS(F$19:F$49,$E$19:$E$49,$E51,$D$19:$D$49,"Special Projects"))*$F$81</f>
-        <v/>
-      </c>
-      <c r="G51" s="49">
-        <f>(SUMIFS(G$19:G$49,$E$19:$E$49,$E51,$D$19:$D$49,"Operations &amp; Support")+SUMIFS(G$19:G$49,$E$19:$E$49,$E51,$D$19:$D$49,"Special Projects"))*$F$81</f>
-        <v/>
-      </c>
-      <c r="H51" s="48">
-        <f>(SUMIFS(H$19:H$49,$E$19:$E$49,$E51,$D$19:$D$49,"Operations &amp; Support")+SUMIFS(H$19:H$49,$E$19:$E$49,$E51,$D$19:$D$49,"Special Projects"))*$F$81</f>
-        <v/>
-      </c>
-      <c r="I51" s="48">
-        <f>(SUMIFS(I$19:I$49,$E$19:$E$49,$E51,$D$19:$D$49,"Operations &amp; Support")+SUMIFS(I$19:I$49,$E$19:$E$49,$E51,$D$19:$D$49,"Special Projects"))*$F$81</f>
-        <v/>
-      </c>
-      <c r="J51" s="48">
-        <f>(SUMIFS(J$19:J$49,$E$19:$E$49,$E51,$D$19:$D$49,"Operations &amp; Support")+SUMIFS(J$19:J$49,$E$19:$E$49,$E51,$D$19:$D$49,"Special Projects"))*$F$81</f>
-        <v/>
-      </c>
-      <c r="K51" s="48">
-        <f>(SUMIFS(K$19:K$49,$E$19:$E$49,$E51,$D$19:$D$49,"Operations &amp; Support")+SUMIFS(K$19:K$49,$E$19:$E$49,$E51,$D$19:$D$49,"Special Projects"))*$F$81</f>
-        <v/>
-      </c>
-      <c r="L51" s="50">
-        <f>SUM(F51+H51+I51+J51+K51)</f>
-        <v/>
-      </c>
-      <c r="M51" s="24">
-        <f>(F51+H51+I51+J51+K51)/5</f>
-        <v/>
-      </c>
+      <c r="F51" s="48" t="n"/>
+      <c r="G51" s="49" t="n"/>
+      <c r="H51" s="48" t="n"/>
+      <c r="I51" s="48" t="n"/>
+      <c r="J51" s="48" t="n"/>
+      <c r="K51" s="48" t="n"/>
+      <c r="L51" s="50" t="n"/>
+      <c r="M51" s="24" t="n"/>
     </row>
     <row r="52" ht="27" customHeight="1">
       <c r="B52" s="200" t="n"/>
@@ -13416,38 +12921,14 @@
           <t>$15M P98</t>
         </is>
       </c>
-      <c r="F52" s="48">
-        <f>(SUMIFS(F$19:F$49,$E$19:$E$49,$E52,$D$19:$D$49,"Operations &amp; Support")+SUMIFS(F$19:F$49,$E$19:$E$49,$E52,$D$19:$D$49,"Special Projects"))*$F$81</f>
-        <v/>
-      </c>
-      <c r="G52" s="49">
-        <f>(SUMIFS(G$19:G$49,$E$19:$E$49,$E52,$D$19:$D$49,"Operations &amp; Support")+SUMIFS(G$19:G$49,$E$19:$E$49,$E52,$D$19:$D$49,"Special Projects"))*$F$81</f>
-        <v/>
-      </c>
-      <c r="H52" s="48">
-        <f>(SUMIFS(H$19:H$49,$E$19:$E$49,$E52,$D$19:$D$49,"Operations &amp; Support")+SUMIFS(H$19:H$49,$E$19:$E$49,$E52,$D$19:$D$49,"Special Projects"))*$F$81</f>
-        <v/>
-      </c>
-      <c r="I52" s="48">
-        <f>(SUMIFS(I$19:I$49,$E$19:$E$49,$E52,$D$19:$D$49,"Operations &amp; Support")+SUMIFS(I$19:I$49,$E$19:$E$49,$E52,$D$19:$D$49,"Special Projects"))*$F$81</f>
-        <v/>
-      </c>
-      <c r="J52" s="48">
-        <f>(SUMIFS(J$19:J$49,$E$19:$E$49,$E52,$D$19:$D$49,"Operations &amp; Support")+SUMIFS(J$19:J$49,$E$19:$E$49,$E52,$D$19:$D$49,"Special Projects"))*$F$81</f>
-        <v/>
-      </c>
-      <c r="K52" s="48">
-        <f>(SUMIFS(K$19:K$49,$E$19:$E$49,$E52,$D$19:$D$49,"Operations &amp; Support")+SUMIFS(K$19:K$49,$E$19:$E$49,$E52,$D$19:$D$49,"Special Projects"))*$F$81</f>
-        <v/>
-      </c>
-      <c r="L52" s="50">
-        <f>SUM(F52+H52+I52+J52+K52)</f>
-        <v/>
-      </c>
-      <c r="M52" s="24">
-        <f>(F52+H52+I52+J52+K52)/5</f>
-        <v/>
-      </c>
+      <c r="F52" s="48" t="n"/>
+      <c r="G52" s="49" t="n"/>
+      <c r="H52" s="48" t="n"/>
+      <c r="I52" s="48" t="n"/>
+      <c r="J52" s="48" t="n"/>
+      <c r="K52" s="48" t="n"/>
+      <c r="L52" s="50" t="n"/>
+      <c r="M52" s="24" t="n"/>
     </row>
     <row r="53">
       <c r="B53" s="36" t="inlineStr">
@@ -13458,38 +12939,14 @@
       <c r="C53" s="37" t="n"/>
       <c r="D53" s="37" t="n"/>
       <c r="E53" s="37" t="n"/>
-      <c r="F53" s="38">
-        <f>SUMIF($D$19:$D$52,$B53,F$19:F$52)</f>
-        <v/>
-      </c>
-      <c r="G53" s="38">
-        <f>SUMIF($D$19:$D$52,$B53,G$19:G$52)</f>
-        <v/>
-      </c>
-      <c r="H53" s="38">
-        <f>SUMIF($D$19:$D$52,$B53,H$19:H$52)</f>
-        <v/>
-      </c>
-      <c r="I53" s="38">
-        <f>SUMIF($D$19:$D$52,$B53,I$19:I$52)</f>
-        <v/>
-      </c>
-      <c r="J53" s="38">
-        <f>SUMIF($D$19:$D$52,$B53,J$19:J$52)</f>
-        <v/>
-      </c>
-      <c r="K53" s="38">
-        <f>SUMIF($D$19:$D$52,$B53,K$19:K$52)</f>
-        <v/>
-      </c>
-      <c r="L53" s="38">
-        <f>L19+L20+L21+L23+L26+L29+L34+L39+L40+L42+L46+L47+L48+L49+L50+L51</f>
-        <v/>
-      </c>
-      <c r="M53" s="39">
-        <f>(F53+H53+I53+J53+K53)/5</f>
-        <v/>
-      </c>
+      <c r="F53" s="38" t="n"/>
+      <c r="G53" s="38" t="n"/>
+      <c r="H53" s="38" t="n"/>
+      <c r="I53" s="38" t="n"/>
+      <c r="J53" s="38" t="n"/>
+      <c r="K53" s="38" t="n"/>
+      <c r="L53" s="38" t="n"/>
+      <c r="M53" s="39" t="n"/>
     </row>
     <row r="54" outlineLevel="1">
       <c r="B54" s="36" t="inlineStr">
@@ -13500,38 +12957,14 @@
       <c r="C54" s="37" t="n"/>
       <c r="D54" s="37" t="n"/>
       <c r="E54" s="37" t="n"/>
-      <c r="F54" s="38">
-        <f>SUMIF($D$19:$D$52,$B54,F$19:F$52)</f>
-        <v/>
-      </c>
-      <c r="G54" s="38">
-        <f>SUMIF($D$19:$D$52,$B54,G$19:G$52)</f>
-        <v/>
-      </c>
-      <c r="H54" s="38">
-        <f>SUMIF($D$19:$D$52,$B54,H$19:H$52)</f>
-        <v/>
-      </c>
-      <c r="I54" s="38">
-        <f>SUMIF($D$19:$D$52,$B54,I$19:I$52)</f>
-        <v/>
-      </c>
-      <c r="J54" s="38">
-        <f>SUMIF($D$19:$D$52,$B54,J$19:J$52)</f>
-        <v/>
-      </c>
-      <c r="K54" s="38">
-        <f>SUMIF($D$19:$D$52,$B54,K$19:K$52)</f>
-        <v/>
-      </c>
-      <c r="L54" s="38">
-        <f>SUM(L23+L32+L33+L36+L43+L45+L37)</f>
-        <v/>
-      </c>
-      <c r="M54" s="39">
-        <f>(F54+H54+I54+J54+K54)/5</f>
-        <v/>
-      </c>
+      <c r="F54" s="38" t="n"/>
+      <c r="G54" s="38" t="n"/>
+      <c r="H54" s="38" t="n"/>
+      <c r="I54" s="38" t="n"/>
+      <c r="J54" s="38" t="n"/>
+      <c r="K54" s="38" t="n"/>
+      <c r="L54" s="38" t="n"/>
+      <c r="M54" s="39" t="n"/>
     </row>
     <row r="55">
       <c r="B55" s="36" t="inlineStr">
@@ -13542,38 +12975,14 @@
       <c r="C55" s="37" t="n"/>
       <c r="D55" s="37" t="n"/>
       <c r="E55" s="37" t="n"/>
-      <c r="F55" s="38">
-        <f>SUMIF($D$19:$D$52,$B55,F$19:F$52)</f>
-        <v/>
-      </c>
-      <c r="G55" s="38">
-        <f>SUMIF($D$19:$D$52,$B55,G$19:G$52)</f>
-        <v/>
-      </c>
-      <c r="H55" s="38">
-        <f>SUMIF($D$19:$D$52,$B55,H$19:H$52)</f>
-        <v/>
-      </c>
-      <c r="I55" s="38">
-        <f>SUMIF($D$19:$D$52,$B55,I$19:I$52)</f>
-        <v/>
-      </c>
-      <c r="J55" s="38">
-        <f>SUMIF($D$19:$D$52,$B55,J$19:J$52)</f>
-        <v/>
-      </c>
-      <c r="K55" s="38">
-        <f>SUMIF($D$19:$D$52,$B55,K$19:K$52)</f>
-        <v/>
-      </c>
-      <c r="L55" s="38">
-        <f>SUM(L41)</f>
-        <v/>
-      </c>
-      <c r="M55" s="39">
-        <f>(F55+H55+I55+J55+K55)/5</f>
-        <v/>
-      </c>
+      <c r="F55" s="38" t="n"/>
+      <c r="G55" s="38" t="n"/>
+      <c r="H55" s="38" t="n"/>
+      <c r="I55" s="38" t="n"/>
+      <c r="J55" s="38" t="n"/>
+      <c r="K55" s="38" t="n"/>
+      <c r="L55" s="38" t="n"/>
+      <c r="M55" s="39" t="n"/>
     </row>
     <row r="56">
       <c r="B56" s="57" t="inlineStr">
@@ -13584,38 +12993,14 @@
       <c r="C56" s="37" t="n"/>
       <c r="D56" s="37" t="n"/>
       <c r="E56" s="37" t="n"/>
-      <c r="F56" s="38">
-        <f>F53+F54+F55</f>
-        <v/>
-      </c>
-      <c r="G56" s="38">
-        <f>G53+G54+G55</f>
-        <v/>
-      </c>
-      <c r="H56" s="38">
-        <f>H53+H54+H55</f>
-        <v/>
-      </c>
-      <c r="I56" s="38">
-        <f>I53+I54+I55</f>
-        <v/>
-      </c>
-      <c r="J56" s="38">
-        <f>J53+J54+J55</f>
-        <v/>
-      </c>
-      <c r="K56" s="38">
-        <f>K53+K54+K55</f>
-        <v/>
-      </c>
-      <c r="L56" s="38">
-        <f>L53+L54+L55</f>
-        <v/>
-      </c>
-      <c r="M56" s="39">
-        <f>(F56+H56+I56+J56+K56)/5</f>
-        <v/>
-      </c>
+      <c r="F56" s="38" t="n"/>
+      <c r="G56" s="38" t="n"/>
+      <c r="H56" s="38" t="n"/>
+      <c r="I56" s="38" t="n"/>
+      <c r="J56" s="38" t="n"/>
+      <c r="K56" s="38" t="n"/>
+      <c r="L56" s="38" t="n"/>
+      <c r="M56" s="39" t="n"/>
     </row>
     <row r="57" ht="6.75" customFormat="1" customHeight="1" s="58">
       <c r="B57" s="59" t="inlineStr">
@@ -13626,31 +13011,13 @@
       <c r="C57" s="60" t="n"/>
       <c r="D57" s="61" t="n"/>
       <c r="E57" s="60" t="n"/>
-      <c r="F57" s="62">
-        <f>F15-F56</f>
-        <v/>
-      </c>
+      <c r="F57" s="62" t="n"/>
       <c r="G57" s="63" t="n"/>
-      <c r="H57" s="62">
-        <f>H15-H56</f>
-        <v/>
-      </c>
-      <c r="I57" s="62">
-        <f>I15-I56</f>
-        <v/>
-      </c>
-      <c r="J57" s="62">
-        <f>J15-J56</f>
-        <v/>
-      </c>
-      <c r="K57" s="62">
-        <f>K15-K56</f>
-        <v/>
-      </c>
-      <c r="L57" s="64">
-        <f>SUM(F57:K57)</f>
-        <v/>
-      </c>
+      <c r="H57" s="62" t="n"/>
+      <c r="I57" s="62" t="n"/>
+      <c r="J57" s="62" t="n"/>
+      <c r="K57" s="62" t="n"/>
+      <c r="L57" s="64" t="n"/>
       <c r="M57" s="65" t="n"/>
     </row>
     <row r="58" ht="6" customFormat="1" customHeight="1" s="58">
@@ -13662,10 +13029,7 @@
           <t>$6M</t>
         </is>
       </c>
-      <c r="F58" s="62">
-        <f>F6+F7</f>
-        <v/>
-      </c>
+      <c r="F58" s="62" t="n"/>
       <c r="G58" s="63" t="n"/>
       <c r="H58" s="62" t="n"/>
       <c r="I58" s="62" t="n"/>
@@ -13737,38 +13101,14 @@
       <c r="C60" s="69" t="n"/>
       <c r="D60" s="70" t="n"/>
       <c r="E60" s="69" t="n"/>
-      <c r="F60" s="69">
-        <f>SUMIF($C$19:$C$52,$B60,F$19:F$52)</f>
-        <v/>
-      </c>
-      <c r="G60" s="71">
-        <f>SUMIF($C$19:$C$52,$B60,G$19:G$52)</f>
-        <v/>
-      </c>
-      <c r="H60" s="69">
-        <f>SUMIF($C$19:$C$52,$B60,H$19:H$52)</f>
-        <v/>
-      </c>
-      <c r="I60" s="69">
-        <f>SUMIF($C$19:$C$52,$B60,I$19:I$52)</f>
-        <v/>
-      </c>
-      <c r="J60" s="69">
-        <f>SUMIF($C$19:$C$52,$B60,J$19:J$52)</f>
-        <v/>
-      </c>
-      <c r="K60" s="69">
-        <f>SUMIF($C$19:$C$52,$B60,K$19:K$52)</f>
-        <v/>
-      </c>
-      <c r="L60" s="72">
-        <f>SUM(F60+H60+I60+J60+K60)</f>
-        <v/>
-      </c>
-      <c r="M60" s="24">
-        <f>(L60)/5</f>
-        <v/>
-      </c>
+      <c r="F60" s="69" t="n"/>
+      <c r="G60" s="71" t="n"/>
+      <c r="H60" s="69" t="n"/>
+      <c r="I60" s="69" t="n"/>
+      <c r="J60" s="69" t="n"/>
+      <c r="K60" s="69" t="n"/>
+      <c r="L60" s="72" t="n"/>
+      <c r="M60" s="24" t="n"/>
     </row>
     <row r="61" ht="15" customFormat="1" customHeight="1" s="58">
       <c r="B61" s="68" t="inlineStr">
@@ -13779,38 +13119,14 @@
       <c r="C61" s="69" t="n"/>
       <c r="D61" s="70" t="n"/>
       <c r="E61" s="69" t="n"/>
-      <c r="F61" s="69">
-        <f>SUMIF($C$19:$C$52,$B61,F$19:F$52)</f>
-        <v/>
-      </c>
-      <c r="G61" s="71">
-        <f>SUMIF($C$19:$C$52,$B61,G$19:G$52)</f>
-        <v/>
-      </c>
-      <c r="H61" s="69">
-        <f>SUMIF($C$19:$C$52,$B61,H$19:H$52)</f>
-        <v/>
-      </c>
-      <c r="I61" s="69">
-        <f>SUMIF($C$19:$C$52,$B61,I$19:I$52)</f>
-        <v/>
-      </c>
-      <c r="J61" s="69">
-        <f>SUMIF($C$19:$C$52,$B61,J$19:J$52)</f>
-        <v/>
-      </c>
-      <c r="K61" s="69">
-        <f>SUMIF($C$19:$C$52,$B61,K$19:K$52)</f>
-        <v/>
-      </c>
-      <c r="L61" s="72">
-        <f>SUM(F61+H61+I61+J61+K61)</f>
-        <v/>
-      </c>
-      <c r="M61" s="24">
-        <f>(F61+H61+I61+J61+K61)/5</f>
-        <v/>
-      </c>
+      <c r="F61" s="69" t="n"/>
+      <c r="G61" s="71" t="n"/>
+      <c r="H61" s="69" t="n"/>
+      <c r="I61" s="69" t="n"/>
+      <c r="J61" s="69" t="n"/>
+      <c r="K61" s="69" t="n"/>
+      <c r="L61" s="72" t="n"/>
+      <c r="M61" s="24" t="n"/>
     </row>
     <row r="62" ht="15" customFormat="1" customHeight="1" s="58">
       <c r="B62" s="68" t="inlineStr">
@@ -13821,38 +13137,14 @@
       <c r="C62" s="69" t="n"/>
       <c r="D62" s="70" t="n"/>
       <c r="E62" s="69" t="n"/>
-      <c r="F62" s="69">
-        <f>SUMIF($C$19:$C$52,$B62,F$19:F$52)</f>
-        <v/>
-      </c>
-      <c r="G62" s="71">
-        <f>SUMIF($C$19:$C$52,$B62,G$19:G$52)</f>
-        <v/>
-      </c>
-      <c r="H62" s="69">
-        <f>SUMIF($C$19:$C$52,$B62,H$19:H$52)</f>
-        <v/>
-      </c>
-      <c r="I62" s="69">
-        <f>SUMIF($C$19:$C$52,$B62,I$19:I$52)</f>
-        <v/>
-      </c>
-      <c r="J62" s="69">
-        <f>SUMIF($C$19:$C$52,$B62,J$19:J$52)</f>
-        <v/>
-      </c>
-      <c r="K62" s="69">
-        <f>SUMIF($C$19:$C$52,$B62,K$19:K$52)</f>
-        <v/>
-      </c>
-      <c r="L62" s="72">
-        <f>SUM(F62+H62+I62+J62+K62)</f>
-        <v/>
-      </c>
-      <c r="M62" s="24">
-        <f>(F62+H62+I62+J62+K62)/5</f>
-        <v/>
-      </c>
+      <c r="F62" s="69" t="n"/>
+      <c r="G62" s="71" t="n"/>
+      <c r="H62" s="69" t="n"/>
+      <c r="I62" s="69" t="n"/>
+      <c r="J62" s="69" t="n"/>
+      <c r="K62" s="69" t="n"/>
+      <c r="L62" s="72" t="n"/>
+      <c r="M62" s="24" t="n"/>
     </row>
     <row r="63" ht="15" customFormat="1" customHeight="1" s="58">
       <c r="B63" s="68" t="inlineStr">
@@ -13863,38 +13155,14 @@
       <c r="C63" s="69" t="n"/>
       <c r="D63" s="70" t="n"/>
       <c r="E63" s="69" t="n"/>
-      <c r="F63" s="69">
-        <f>SUMIF($C$19:$C$52,$B63,F$19:F$52)</f>
-        <v/>
-      </c>
-      <c r="G63" s="71">
-        <f>SUMIF($C$19:$C$52,$B63,G$19:G$52)</f>
-        <v/>
-      </c>
-      <c r="H63" s="69">
-        <f>SUMIF($C$19:$C$52,$B63,H$19:H$52)</f>
-        <v/>
-      </c>
-      <c r="I63" s="69">
-        <f>SUMIF($C$19:$C$52,$B63,I$19:I$52)</f>
-        <v/>
-      </c>
-      <c r="J63" s="69">
-        <f>SUMIF($C$19:$C$52,$B63,J$19:J$52)</f>
-        <v/>
-      </c>
-      <c r="K63" s="69">
-        <f>SUMIF($C$19:$C$52,$B63,K$19:K$52)</f>
-        <v/>
-      </c>
-      <c r="L63" s="72">
-        <f>SUM(F63+H63+I63+J63+K63)</f>
-        <v/>
-      </c>
-      <c r="M63" s="24">
-        <f>(F63+H63+I63+J63+K63)/5</f>
-        <v/>
-      </c>
+      <c r="F63" s="69" t="n"/>
+      <c r="G63" s="71" t="n"/>
+      <c r="H63" s="69" t="n"/>
+      <c r="I63" s="69" t="n"/>
+      <c r="J63" s="69" t="n"/>
+      <c r="K63" s="69" t="n"/>
+      <c r="L63" s="72" t="n"/>
+      <c r="M63" s="24" t="n"/>
     </row>
     <row r="64" ht="15" customFormat="1" customHeight="1" s="58">
       <c r="B64" s="68" t="inlineStr">
@@ -13905,38 +13173,14 @@
       <c r="C64" s="69" t="n"/>
       <c r="D64" s="70" t="n"/>
       <c r="E64" s="69" t="n"/>
-      <c r="F64" s="69">
-        <f>SUMIF($C$19:$C$52,$B64,F$19:F$52)</f>
-        <v/>
-      </c>
-      <c r="G64" s="71">
-        <f>SUMIF($C$19:$C$52,$B64,G$19:G$52)</f>
-        <v/>
-      </c>
-      <c r="H64" s="69">
-        <f>SUMIF($C$19:$C$52,$B64,H$19:H$52)</f>
-        <v/>
-      </c>
-      <c r="I64" s="69">
-        <f>SUMIF($C$19:$C$52,$B64,I$19:I$52)</f>
-        <v/>
-      </c>
-      <c r="J64" s="69">
-        <f>SUMIF($C$19:$C$52,$B64,J$19:J$52)</f>
-        <v/>
-      </c>
-      <c r="K64" s="69">
-        <f>SUMIF($C$19:$C$52,$B64,K$19:K$52)</f>
-        <v/>
-      </c>
-      <c r="L64" s="72">
-        <f>SUM(F64+H64+I64+J64+K64)</f>
-        <v/>
-      </c>
-      <c r="M64" s="24">
-        <f>(F64+H64+I64+J64+K64)/5</f>
-        <v/>
-      </c>
+      <c r="F64" s="69" t="n"/>
+      <c r="G64" s="71" t="n"/>
+      <c r="H64" s="69" t="n"/>
+      <c r="I64" s="69" t="n"/>
+      <c r="J64" s="69" t="n"/>
+      <c r="K64" s="69" t="n"/>
+      <c r="L64" s="72" t="n"/>
+      <c r="M64" s="24" t="n"/>
     </row>
     <row r="65" ht="15" customFormat="1" customHeight="1" s="58">
       <c r="B65" s="68" t="inlineStr">
@@ -13947,38 +13191,14 @@
       <c r="C65" s="69" t="n"/>
       <c r="D65" s="70" t="n"/>
       <c r="E65" s="69" t="n"/>
-      <c r="F65" s="69">
-        <f>SUMIF($C$19:$C$52,$B65,F$19:F$52)</f>
-        <v/>
-      </c>
-      <c r="G65" s="71">
-        <f>SUMIF($C$19:$C$52,$B65,G$19:G$52)</f>
-        <v/>
-      </c>
-      <c r="H65" s="69">
-        <f>SUMIF($C$19:$C$52,$B65,H$19:H$52)</f>
-        <v/>
-      </c>
-      <c r="I65" s="69">
-        <f>SUMIF($C$19:$C$52,$B65,I$19:I$52)</f>
-        <v/>
-      </c>
-      <c r="J65" s="69">
-        <f>SUMIF($C$19:$C$52,$B65,J$19:J$52)</f>
-        <v/>
-      </c>
-      <c r="K65" s="69">
-        <f>SUMIF($C$19:$C$52,$B65,K$19:K$52)</f>
-        <v/>
-      </c>
-      <c r="L65" s="72">
-        <f>SUM(F65+H65+I65+J65+K65)</f>
-        <v/>
-      </c>
-      <c r="M65" s="24">
-        <f>(F65+H65+I65+J65+K65)/5</f>
-        <v/>
-      </c>
+      <c r="F65" s="69" t="n"/>
+      <c r="G65" s="71" t="n"/>
+      <c r="H65" s="69" t="n"/>
+      <c r="I65" s="69" t="n"/>
+      <c r="J65" s="69" t="n"/>
+      <c r="K65" s="69" t="n"/>
+      <c r="L65" s="72" t="n"/>
+      <c r="M65" s="24" t="n"/>
     </row>
     <row r="66" ht="15" customFormat="1" customHeight="1" s="58">
       <c r="B66" s="68" t="inlineStr">
@@ -13989,38 +13209,14 @@
       <c r="C66" s="69" t="n"/>
       <c r="D66" s="70" t="n"/>
       <c r="E66" s="69" t="n"/>
-      <c r="F66" s="69">
-        <f>SUMIF($C$19:$C$52,$B66,F$19:F$52)</f>
-        <v/>
-      </c>
-      <c r="G66" s="71">
-        <f>SUMIF($C$19:$C$52,$B66,G$19:G$52)</f>
-        <v/>
-      </c>
-      <c r="H66" s="69">
-        <f>SUMIF($C$19:$C$52,$B66,H$19:H$52)</f>
-        <v/>
-      </c>
-      <c r="I66" s="69">
-        <f>SUMIF($C$19:$C$52,$B66,I$19:I$52)</f>
-        <v/>
-      </c>
-      <c r="J66" s="69">
-        <f>SUMIF($C$19:$C$52,$B66,J$19:J$52)</f>
-        <v/>
-      </c>
-      <c r="K66" s="69">
-        <f>SUMIF($C$19:$C$52,$B66,K$19:K$52)</f>
-        <v/>
-      </c>
-      <c r="L66" s="72">
-        <f>SUM(F66+H66+I66+J66+K66)</f>
-        <v/>
-      </c>
-      <c r="M66" s="24">
-        <f>(F66+H66+I66+J66+K66)/5</f>
-        <v/>
-      </c>
+      <c r="F66" s="69" t="n"/>
+      <c r="G66" s="71" t="n"/>
+      <c r="H66" s="69" t="n"/>
+      <c r="I66" s="69" t="n"/>
+      <c r="J66" s="69" t="n"/>
+      <c r="K66" s="69" t="n"/>
+      <c r="L66" s="72" t="n"/>
+      <c r="M66" s="24" t="n"/>
     </row>
     <row r="67" ht="15" customFormat="1" customHeight="1" s="58">
       <c r="B67" s="68" t="inlineStr">
@@ -14031,38 +13227,14 @@
       <c r="C67" s="69" t="n"/>
       <c r="D67" s="70" t="n"/>
       <c r="E67" s="69" t="n"/>
-      <c r="F67" s="69">
-        <f>SUMIF($C$19:$C$52,$B67,F$19:F$52)</f>
-        <v/>
-      </c>
-      <c r="G67" s="71">
-        <f>SUMIF($C$19:$C$52,$B67,G$19:G$52)</f>
-        <v/>
-      </c>
-      <c r="H67" s="69">
-        <f>SUMIF($C$19:$C$52,$B67,H$19:H$52)</f>
-        <v/>
-      </c>
-      <c r="I67" s="69">
-        <f>SUMIF($C$19:$C$52,$B67,I$19:I$52)</f>
-        <v/>
-      </c>
-      <c r="J67" s="69">
-        <f>SUMIF($C$19:$C$52,$B67,J$19:J$52)</f>
-        <v/>
-      </c>
-      <c r="K67" s="69">
-        <f>SUMIF($C$19:$C$52,$B67,K$19:K$52)</f>
-        <v/>
-      </c>
-      <c r="L67" s="72">
-        <f>SUM(F67+H67+I67+J67+K67)</f>
-        <v/>
-      </c>
-      <c r="M67" s="24">
-        <f>(F67+H67+I67+J67+K67)/5</f>
-        <v/>
-      </c>
+      <c r="F67" s="69" t="n"/>
+      <c r="G67" s="71" t="n"/>
+      <c r="H67" s="69" t="n"/>
+      <c r="I67" s="69" t="n"/>
+      <c r="J67" s="69" t="n"/>
+      <c r="K67" s="69" t="n"/>
+      <c r="L67" s="72" t="n"/>
+      <c r="M67" s="24" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="58" t="n"/>
@@ -14140,38 +13312,14 @@
       <c r="C70" s="69" t="n"/>
       <c r="D70" s="70" t="n"/>
       <c r="E70" s="69" t="n"/>
-      <c r="F70" s="69">
-        <f>SUMIF($D$19:$D$52,$B70,F$19:F$52)</f>
-        <v/>
-      </c>
-      <c r="G70" s="71">
-        <f>SUMIF($D$19:$D$52,$B70,G$19:G$52)</f>
-        <v/>
-      </c>
-      <c r="H70" s="69">
-        <f>SUMIF($D$19:$D$52,$B70,H$19:H$52)</f>
-        <v/>
-      </c>
-      <c r="I70" s="69">
-        <f>SUMIF($D$19:$D$52,$B70,I$19:I$52)</f>
-        <v/>
-      </c>
-      <c r="J70" s="69">
-        <f>SUMIF($D$19:$D$52,$B70,J$19:J$52)</f>
-        <v/>
-      </c>
-      <c r="K70" s="69">
-        <f>SUMIF($D$19:$D$52,$B70,K$19:K$52)</f>
-        <v/>
-      </c>
-      <c r="L70" s="72">
-        <f>SUM(F70+H70+I70+J70+K70)</f>
-        <v/>
-      </c>
-      <c r="M70" s="24">
-        <f>(L70)/5</f>
-        <v/>
-      </c>
+      <c r="F70" s="69" t="n"/>
+      <c r="G70" s="71" t="n"/>
+      <c r="H70" s="69" t="n"/>
+      <c r="I70" s="69" t="n"/>
+      <c r="J70" s="69" t="n"/>
+      <c r="K70" s="69" t="n"/>
+      <c r="L70" s="72" t="n"/>
+      <c r="M70" s="24" t="n"/>
     </row>
     <row r="71" ht="15" customFormat="1" customHeight="1" s="58">
       <c r="B71" s="68" t="inlineStr">
@@ -14182,38 +13330,14 @@
       <c r="C71" s="69" t="n"/>
       <c r="D71" s="70" t="n"/>
       <c r="E71" s="69" t="n"/>
-      <c r="F71" s="69">
-        <f>SUMIF($D$19:$D$52,$B71,F$19:F$52)</f>
-        <v/>
-      </c>
-      <c r="G71" s="71">
-        <f>SUMIF($D$19:$D$52,$B71,G$19:G$52)</f>
-        <v/>
-      </c>
-      <c r="H71" s="69">
-        <f>SUMIF($D$19:$D$52,$B71,H$19:H$52)</f>
-        <v/>
-      </c>
-      <c r="I71" s="69">
-        <f>SUMIF($D$19:$D$52,$B71,I$19:I$52)</f>
-        <v/>
-      </c>
-      <c r="J71" s="69">
-        <f>SUMIF($D$19:$D$52,$B71,J$19:J$52)</f>
-        <v/>
-      </c>
-      <c r="K71" s="69">
-        <f>SUMIF($D$19:$D$52,$B71,K$19:K$52)</f>
-        <v/>
-      </c>
-      <c r="L71" s="72">
-        <f>SUM(F71+H71+I71+J71+K71)</f>
-        <v/>
-      </c>
-      <c r="M71" s="24">
-        <f>(L71)/5</f>
-        <v/>
-      </c>
+      <c r="F71" s="69" t="n"/>
+      <c r="G71" s="71" t="n"/>
+      <c r="H71" s="69" t="n"/>
+      <c r="I71" s="69" t="n"/>
+      <c r="J71" s="69" t="n"/>
+      <c r="K71" s="69" t="n"/>
+      <c r="L71" s="72" t="n"/>
+      <c r="M71" s="24" t="n"/>
     </row>
     <row r="72" ht="15" customFormat="1" customHeight="1" s="58">
       <c r="B72" s="68" t="inlineStr">
@@ -14224,38 +13348,14 @@
       <c r="C72" s="69" t="n"/>
       <c r="D72" s="70" t="n"/>
       <c r="E72" s="69" t="n"/>
-      <c r="F72" s="69">
-        <f>SUMIF($D$19:$D$52,$B72,F$19:F$52)</f>
-        <v/>
-      </c>
-      <c r="G72" s="71">
-        <f>SUMIF($D$19:$D$52,$B72,G$19:G$52)</f>
-        <v/>
-      </c>
-      <c r="H72" s="69">
-        <f>SUMIF($D$19:$D$52,$B72,H$19:H$52)</f>
-        <v/>
-      </c>
-      <c r="I72" s="69">
-        <f>SUMIF($D$19:$D$52,$B72,I$19:I$52)</f>
-        <v/>
-      </c>
-      <c r="J72" s="69">
-        <f>SUMIF($D$19:$D$52,$B72,J$19:J$52)</f>
-        <v/>
-      </c>
-      <c r="K72" s="69">
-        <f>SUMIF($D$19:$D$52,$B72,K$19:K$52)</f>
-        <v/>
-      </c>
-      <c r="L72" s="72">
-        <f>SUM(F72+H72+I72+J72+K72)</f>
-        <v/>
-      </c>
-      <c r="M72" s="24">
-        <f>(L72)/5</f>
-        <v/>
-      </c>
+      <c r="F72" s="69" t="n"/>
+      <c r="G72" s="71" t="n"/>
+      <c r="H72" s="69" t="n"/>
+      <c r="I72" s="69" t="n"/>
+      <c r="J72" s="69" t="n"/>
+      <c r="K72" s="69" t="n"/>
+      <c r="L72" s="72" t="n"/>
+      <c r="M72" s="24" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="58" t="n"/>
@@ -14297,27 +13397,12 @@
       <c r="C75" s="81" t="n"/>
       <c r="D75" s="81" t="n"/>
       <c r="E75" s="81" t="n"/>
-      <c r="F75" s="82">
-        <f>F100</f>
-        <v/>
-      </c>
+      <c r="F75" s="82" t="n"/>
       <c r="G75" s="203" t="n"/>
-      <c r="H75" s="82">
-        <f>H100</f>
-        <v/>
-      </c>
-      <c r="I75" s="82">
-        <f>I100</f>
-        <v/>
-      </c>
-      <c r="J75" s="82">
-        <f>J100</f>
-        <v/>
-      </c>
-      <c r="K75" s="82">
-        <f>K100</f>
-        <v/>
-      </c>
+      <c r="H75" s="82" t="n"/>
+      <c r="I75" s="82" t="n"/>
+      <c r="J75" s="82" t="n"/>
+      <c r="K75" s="82" t="n"/>
       <c r="L75" s="83" t="inlineStr">
         <is>
           <t>TOTAL</t>
@@ -14333,31 +13418,13 @@
       <c r="C76" s="206" t="n"/>
       <c r="D76" s="206" t="n"/>
       <c r="E76" s="206" t="n"/>
-      <c r="F76" s="48">
-        <f>1000000+230000</f>
-        <v/>
-      </c>
+      <c r="F76" s="48" t="n"/>
       <c r="G76" s="196" t="n"/>
-      <c r="H76" s="48">
-        <f>1000000+240000</f>
-        <v/>
-      </c>
-      <c r="I76" s="48">
-        <f>1000000+250000</f>
-        <v/>
-      </c>
-      <c r="J76" s="48">
-        <f>1000000+260000</f>
-        <v/>
-      </c>
-      <c r="K76" s="48">
-        <f>1000000+270000</f>
-        <v/>
-      </c>
-      <c r="L76" s="23">
-        <f>SUM(F76:K76)</f>
-        <v/>
-      </c>
+      <c r="H76" s="48" t="n"/>
+      <c r="I76" s="48" t="n"/>
+      <c r="J76" s="48" t="n"/>
+      <c r="K76" s="48" t="n"/>
+      <c r="L76" s="23" t="n"/>
     </row>
     <row r="77">
       <c r="B77" s="84" t="inlineStr">
@@ -14368,31 +13435,13 @@
       <c r="C77" s="206" t="n"/>
       <c r="D77" s="206" t="n"/>
       <c r="E77" s="206" t="n"/>
-      <c r="F77" s="48">
-        <f>1300000</f>
-        <v/>
-      </c>
+      <c r="F77" s="48" t="n"/>
       <c r="G77" s="196" t="n"/>
-      <c r="H77" s="48">
-        <f>1400000</f>
-        <v/>
-      </c>
-      <c r="I77" s="48">
-        <f>1500000</f>
-        <v/>
-      </c>
-      <c r="J77" s="48">
-        <f>1600000</f>
-        <v/>
-      </c>
-      <c r="K77" s="48">
-        <f>1700000</f>
-        <v/>
-      </c>
-      <c r="L77" s="23">
-        <f>SUM(F77:K77)</f>
-        <v/>
-      </c>
+      <c r="H77" s="48" t="n"/>
+      <c r="I77" s="48" t="n"/>
+      <c r="J77" s="48" t="n"/>
+      <c r="K77" s="48" t="n"/>
+      <c r="L77" s="23" t="n"/>
     </row>
     <row r="78" customFormat="1" s="85">
       <c r="B78" s="86" t="inlineStr">
@@ -14627,10 +13676,7 @@
       <c r="F87" s="101" t="n">
         <v>1</v>
       </c>
-      <c r="G87" s="102">
-        <f>Positions!K2</f>
-        <v/>
-      </c>
+      <c r="G87" s="102" t="n"/>
       <c r="H87" s="101" t="n">
         <v>1</v>
       </c>
@@ -14659,10 +13705,7 @@
       <c r="F88" s="101" t="n">
         <v>1</v>
       </c>
-      <c r="G88" s="102">
-        <f>Positions!K3</f>
-        <v/>
-      </c>
+      <c r="G88" s="102" t="n"/>
       <c r="H88" s="101" t="n">
         <v>1</v>
       </c>
@@ -14691,10 +13734,7 @@
       <c r="F89" s="101" t="n">
         <v>1</v>
       </c>
-      <c r="G89" s="102">
-        <f>Positions!K4</f>
-        <v/>
-      </c>
+      <c r="G89" s="102" t="n"/>
       <c r="H89" s="101" t="n">
         <v>1</v>
       </c>
@@ -14723,10 +13763,7 @@
       <c r="F90" s="101" t="n">
         <v>1</v>
       </c>
-      <c r="G90" s="102">
-        <f>Positions!K5</f>
-        <v/>
-      </c>
+      <c r="G90" s="102" t="n"/>
       <c r="H90" s="101" t="n">
         <v>1</v>
       </c>
@@ -14755,10 +13792,7 @@
       <c r="F91" s="101" t="n">
         <v>1</v>
       </c>
-      <c r="G91" s="102">
-        <f>Positions!K6</f>
-        <v/>
-      </c>
+      <c r="G91" s="102" t="n"/>
       <c r="H91" s="101" t="n">
         <v>1</v>
       </c>
@@ -14787,10 +13821,7 @@
       <c r="F92" s="101" t="n">
         <v>1.5</v>
       </c>
-      <c r="G92" s="102">
-        <f>Positions!K7</f>
-        <v/>
-      </c>
+      <c r="G92" s="102" t="n"/>
       <c r="H92" s="101" t="n">
         <v>1.5</v>
       </c>
@@ -14818,10 +13849,7 @@
       <c r="F93" s="101" t="n">
         <v>1</v>
       </c>
-      <c r="G93" s="102">
-        <f>Positions!K8</f>
-        <v/>
-      </c>
+      <c r="G93" s="102" t="n"/>
       <c r="H93" s="101" t="n">
         <v>1</v>
       </c>
@@ -14849,10 +13877,7 @@
       <c r="F94" s="101" t="n">
         <v>1.5</v>
       </c>
-      <c r="G94" s="102">
-        <f>Positions!K9</f>
-        <v/>
-      </c>
+      <c r="G94" s="102" t="n"/>
       <c r="H94" s="101" t="n">
         <v>1.5</v>
       </c>
@@ -14880,10 +13905,7 @@
       <c r="F95" s="104" t="n">
         <v>1</v>
       </c>
-      <c r="G95" s="102">
-        <f>Positions!K10</f>
-        <v/>
-      </c>
+      <c r="G95" s="102" t="n"/>
       <c r="H95" s="104" t="n">
         <v>1</v>
       </c>
@@ -14911,10 +13933,7 @@
       <c r="F96" s="101" t="n">
         <v>1</v>
       </c>
-      <c r="G96" s="102">
-        <f>Positions!K11</f>
-        <v/>
-      </c>
+      <c r="G96" s="102" t="n"/>
       <c r="H96" s="101" t="n">
         <v>1</v>
       </c>
@@ -14943,10 +13962,7 @@
       <c r="F97" s="101" t="n">
         <v>2</v>
       </c>
-      <c r="G97" s="102">
-        <f>Positions!K12</f>
-        <v/>
-      </c>
+      <c r="G97" s="102" t="n"/>
       <c r="H97" s="101" t="n">
         <v>2</v>
       </c>
@@ -14974,10 +13990,7 @@
       <c r="F98" s="101" t="n">
         <v>0.67</v>
       </c>
-      <c r="G98" s="102">
-        <f>Positions!K13</f>
-        <v/>
-      </c>
+      <c r="G98" s="102" t="n"/>
       <c r="H98" s="101" t="n">
         <v>1</v>
       </c>
@@ -15033,30 +14046,12 @@
       <c r="C100" s="192" t="n"/>
       <c r="D100" s="192" t="n"/>
       <c r="E100" s="193" t="n"/>
-      <c r="F100" s="105">
-        <f>SUM(F87:F99)</f>
-        <v/>
-      </c>
-      <c r="G100" s="106">
-        <f>Positions!K15</f>
-        <v/>
-      </c>
-      <c r="H100" s="105">
-        <f>SUM(H87:H99)</f>
-        <v/>
-      </c>
-      <c r="I100" s="105">
-        <f>SUM(I87:I99)</f>
-        <v/>
-      </c>
-      <c r="J100" s="105">
-        <f>SUM(J87:J99)</f>
-        <v/>
-      </c>
-      <c r="K100" s="105">
-        <f>SUM(K87:K99)</f>
-        <v/>
-      </c>
+      <c r="F100" s="105" t="n"/>
+      <c r="G100" s="106" t="n"/>
+      <c r="H100" s="105" t="n"/>
+      <c r="I100" s="105" t="n"/>
+      <c r="J100" s="105" t="n"/>
+      <c r="K100" s="105" t="n"/>
       <c r="L100" s="103" t="n"/>
     </row>
     <row r="101" ht="15" customFormat="1" customHeight="1" s="77">
@@ -15069,30 +14064,12 @@
       <c r="C101" s="192" t="n"/>
       <c r="D101" s="192" t="n"/>
       <c r="E101" s="193" t="n"/>
-      <c r="F101" s="107">
-        <f>Positions!L15</f>
-        <v/>
-      </c>
-      <c r="G101" s="108">
-        <f>Positions!L15</f>
-        <v/>
-      </c>
-      <c r="H101" s="107">
-        <f>H103*0.1</f>
-        <v/>
-      </c>
-      <c r="I101" s="107">
-        <f>I103*0.1</f>
-        <v/>
-      </c>
-      <c r="J101" s="107">
-        <f>J103*0.1</f>
-        <v/>
-      </c>
-      <c r="K101" s="107">
-        <f>K103*0.1</f>
-        <v/>
-      </c>
+      <c r="F101" s="107" t="n"/>
+      <c r="G101" s="108" t="n"/>
+      <c r="H101" s="107" t="n"/>
+      <c r="I101" s="107" t="n"/>
+      <c r="J101" s="107" t="n"/>
+      <c r="K101" s="107" t="n"/>
       <c r="L101" s="103" t="n"/>
     </row>
     <row r="102" ht="15" customFormat="1" customHeight="1" s="77">
@@ -15105,30 +14082,12 @@
       <c r="C102" s="192" t="n"/>
       <c r="D102" s="192" t="n"/>
       <c r="E102" s="193" t="n"/>
-      <c r="F102" s="109">
-        <f>G103/F100</f>
-        <v/>
-      </c>
-      <c r="G102" s="106">
-        <f>G103/F100</f>
-        <v/>
-      </c>
-      <c r="H102" s="109">
-        <f>G102*(1+H80)</f>
-        <v/>
-      </c>
-      <c r="I102" s="109">
-        <f>H102*(1+I80)</f>
-        <v/>
-      </c>
-      <c r="J102" s="109">
-        <f>I102*(1+J80)</f>
-        <v/>
-      </c>
-      <c r="K102" s="109">
-        <f>J102*(1+K80)</f>
-        <v/>
-      </c>
+      <c r="F102" s="109" t="n"/>
+      <c r="G102" s="106" t="n"/>
+      <c r="H102" s="109" t="n"/>
+      <c r="I102" s="109" t="n"/>
+      <c r="J102" s="109" t="n"/>
+      <c r="K102" s="109" t="n"/>
       <c r="L102" s="103" t="n"/>
     </row>
     <row r="103" ht="15" customFormat="1" customHeight="1" s="77">
@@ -15141,30 +14100,12 @@
       <c r="C103" s="192" t="n"/>
       <c r="D103" s="192" t="n"/>
       <c r="E103" s="193" t="n"/>
-      <c r="F103" s="107">
-        <f>G100+G101</f>
-        <v/>
-      </c>
-      <c r="G103" s="108">
-        <f>G100+G101</f>
-        <v/>
-      </c>
-      <c r="H103" s="107">
-        <f>SUM(G102*(1+H80))*H100</f>
-        <v/>
-      </c>
-      <c r="I103" s="107">
-        <f>SUM(H102*(1+I80))*I100</f>
-        <v/>
-      </c>
-      <c r="J103" s="107">
-        <f>SUM(I102*(1+J80))*J100</f>
-        <v/>
-      </c>
-      <c r="K103" s="107">
-        <f>SUM(J102*(1+K80))*K100</f>
-        <v/>
-      </c>
+      <c r="F103" s="107" t="n"/>
+      <c r="G103" s="108" t="n"/>
+      <c r="H103" s="107" t="n"/>
+      <c r="I103" s="107" t="n"/>
+      <c r="J103" s="107" t="n"/>
+      <c r="K103" s="107" t="n"/>
       <c r="L103" s="103" t="n"/>
     </row>
   </sheetData>
@@ -15429,10 +14370,7 @@
       <c r="E2" s="126" t="n">
         <v>242110</v>
       </c>
-      <c r="F2" s="127">
-        <f>E2*1.15</f>
-        <v/>
-      </c>
+      <c r="F2" s="127" t="n"/>
       <c r="G2" s="128" t="n">
         <v>92663</v>
       </c>
@@ -15447,18 +14385,9 @@
       <c r="J2" s="130" t="n">
         <v>1170</v>
       </c>
-      <c r="K2" s="131">
-        <f>E2+G2</f>
-        <v/>
-      </c>
-      <c r="L2" s="131">
-        <f>K2*0.1</f>
-        <v/>
-      </c>
-      <c r="M2" s="131">
-        <f>SUM(K2:L2)</f>
-        <v/>
-      </c>
+      <c r="K2" s="131" t="n"/>
+      <c r="L2" s="131" t="n"/>
+      <c r="M2" s="131" t="n"/>
     </row>
     <row r="3" ht="51" customHeight="1">
       <c r="A3" s="123" t="inlineStr">
@@ -15482,10 +14411,7 @@
       <c r="E3" s="126" t="n">
         <v>185925</v>
       </c>
-      <c r="F3" s="127">
-        <f>E3*1.15</f>
-        <v/>
-      </c>
+      <c r="F3" s="127" t="n"/>
       <c r="G3" s="128" t="n">
         <v>89377</v>
       </c>
@@ -15500,18 +14426,9 @@
       <c r="J3" s="130" t="n">
         <v>1218</v>
       </c>
-      <c r="K3" s="131">
-        <f>F3</f>
-        <v/>
-      </c>
-      <c r="L3" s="131">
-        <f>K3*0.1</f>
-        <v/>
-      </c>
-      <c r="M3" s="131">
-        <f>SUM(K3:L3)</f>
-        <v/>
-      </c>
+      <c r="K3" s="131" t="n"/>
+      <c r="L3" s="131" t="n"/>
+      <c r="M3" s="131" t="n"/>
     </row>
     <row r="4" ht="50.25" customHeight="1">
       <c r="A4" s="123" t="inlineStr">
@@ -15535,10 +14452,7 @@
       <c r="E4" s="126" t="n">
         <v>183940</v>
       </c>
-      <c r="F4" s="127">
-        <f>E4*1.15</f>
-        <v/>
-      </c>
+      <c r="F4" s="127" t="n"/>
       <c r="G4" s="128" t="n">
         <v>89377</v>
       </c>
@@ -15553,18 +14467,9 @@
       <c r="J4" s="130" t="n">
         <v>1219</v>
       </c>
-      <c r="K4" s="131">
-        <f>F4</f>
-        <v/>
-      </c>
-      <c r="L4" s="131">
-        <f>K4*0.1</f>
-        <v/>
-      </c>
-      <c r="M4" s="131">
-        <f>SUM(K4:L4)</f>
-        <v/>
-      </c>
+      <c r="K4" s="131" t="n"/>
+      <c r="L4" s="131" t="n"/>
+      <c r="M4" s="131" t="n"/>
     </row>
     <row r="5" ht="35.25" customHeight="1">
       <c r="A5" s="123" t="inlineStr">
@@ -15588,10 +14493,7 @@
       <c r="E5" s="126" t="n">
         <v>175276</v>
       </c>
-      <c r="F5" s="127">
-        <f>E5*1.15</f>
-        <v/>
-      </c>
+      <c r="F5" s="127" t="n"/>
       <c r="G5" s="128" t="n">
         <v>89377</v>
       </c>
@@ -15606,18 +14508,9 @@
       <c r="J5" s="130" t="n">
         <v>2118</v>
       </c>
-      <c r="K5" s="131">
-        <f>F5</f>
-        <v/>
-      </c>
-      <c r="L5" s="131">
-        <f>K5*0.1</f>
-        <v/>
-      </c>
-      <c r="M5" s="131">
-        <f>SUM(K5:L5)</f>
-        <v/>
-      </c>
+      <c r="K5" s="131" t="n"/>
+      <c r="L5" s="131" t="n"/>
+      <c r="M5" s="131" t="n"/>
     </row>
     <row r="6" ht="51.75" customHeight="1">
       <c r="A6" s="123" t="inlineStr">
@@ -15641,10 +14534,7 @@
       <c r="E6" s="126" t="n">
         <v>129656</v>
       </c>
-      <c r="F6" s="127">
-        <f>E6*1.15</f>
-        <v/>
-      </c>
+      <c r="F6" s="127" t="n"/>
       <c r="G6" s="128" t="n">
         <v>75085</v>
       </c>
@@ -15659,18 +14549,9 @@
       <c r="J6" s="130" t="n">
         <v>2119</v>
       </c>
-      <c r="K6" s="131">
-        <f>F6</f>
-        <v/>
-      </c>
-      <c r="L6" s="131">
-        <f>K6*0.1</f>
-        <v/>
-      </c>
-      <c r="M6" s="131">
-        <f>SUM(K6:L6)</f>
-        <v/>
-      </c>
+      <c r="K6" s="131" t="n"/>
+      <c r="L6" s="131" t="n"/>
+      <c r="M6" s="131" t="n"/>
     </row>
     <row r="7" ht="51.75" customHeight="1">
       <c r="A7" s="123" t="inlineStr">
@@ -15694,10 +14575,7 @@
       <c r="E7" s="126" t="n">
         <v>168933</v>
       </c>
-      <c r="F7" s="127">
-        <f>E7*1.15</f>
-        <v/>
-      </c>
+      <c r="F7" s="127" t="n"/>
       <c r="G7" s="128" t="n">
         <v>89377</v>
       </c>
@@ -15712,18 +14590,9 @@
       <c r="J7" s="130" t="n">
         <v>2339</v>
       </c>
-      <c r="K7" s="131">
-        <f>F7</f>
-        <v/>
-      </c>
-      <c r="L7" s="131">
-        <f>K7*0.1</f>
-        <v/>
-      </c>
-      <c r="M7" s="131">
-        <f>SUM(K7:L7)</f>
-        <v/>
-      </c>
+      <c r="K7" s="131" t="n"/>
+      <c r="L7" s="131" t="n"/>
+      <c r="M7" s="131" t="n"/>
     </row>
     <row r="8" ht="36" customHeight="1">
       <c r="A8" s="123" t="inlineStr">
@@ -15744,18 +14613,9 @@
           <t>Classified Full-Time Staff</t>
         </is>
       </c>
-      <c r="E8" s="126">
-        <f>(82764/12)*3</f>
-        <v/>
-      </c>
-      <c r="F8" s="127">
-        <f>E8*1.15</f>
-        <v/>
-      </c>
-      <c r="G8" s="128">
-        <f>F8*40%</f>
-        <v/>
-      </c>
+      <c r="E8" s="126" t="n"/>
+      <c r="F8" s="127" t="n"/>
+      <c r="G8" s="128" t="n"/>
       <c r="H8" s="129" t="inlineStr">
         <is>
           <t>R</t>
@@ -15767,18 +14627,9 @@
       <c r="J8" s="130" t="n">
         <v>3000</v>
       </c>
-      <c r="K8" s="131">
-        <f>F8</f>
-        <v/>
-      </c>
-      <c r="L8" s="131">
-        <f>K8*0.1</f>
-        <v/>
-      </c>
-      <c r="M8" s="131">
-        <f>SUM(K8:L8)</f>
-        <v/>
-      </c>
+      <c r="K8" s="131" t="n"/>
+      <c r="L8" s="131" t="n"/>
+      <c r="M8" s="131" t="n"/>
     </row>
     <row r="9" ht="35.25" customHeight="1">
       <c r="A9" s="123" t="inlineStr">
@@ -15802,10 +14653,7 @@
       <c r="E9" s="126" t="n">
         <v>145555</v>
       </c>
-      <c r="F9" s="127">
-        <f>E9*1.15</f>
-        <v/>
-      </c>
+      <c r="F9" s="127" t="n"/>
       <c r="G9" s="128" t="n">
         <v>89377</v>
       </c>
@@ -15822,18 +14670,9 @@
           <t>5910 (Indirect Costs, 9%)  Revenue w/o ITPI, $4,125,000</t>
         </is>
       </c>
-      <c r="K9" s="131">
-        <f>F9</f>
-        <v/>
-      </c>
-      <c r="L9" s="131">
-        <f>K9*0.1</f>
-        <v/>
-      </c>
-      <c r="M9" s="131">
-        <f>SUM(K9:L9)</f>
-        <v/>
-      </c>
+      <c r="K9" s="131" t="n"/>
+      <c r="L9" s="131" t="n"/>
+      <c r="M9" s="131" t="n"/>
     </row>
     <row r="10" ht="33.75" customHeight="1">
       <c r="A10" s="123" t="inlineStr">
@@ -15857,14 +14696,8 @@
       <c r="E10" s="126" t="n">
         <v>80904</v>
       </c>
-      <c r="F10" s="127">
-        <f>E10*1.15</f>
-        <v/>
-      </c>
-      <c r="G10" s="128">
-        <f>F10*0.6</f>
-        <v/>
-      </c>
+      <c r="F10" s="127" t="n"/>
+      <c r="G10" s="128" t="n"/>
       <c r="H10" s="129" t="inlineStr">
         <is>
           <t>M Step 1</t>
@@ -15874,18 +14707,9 @@
         <v>2119</v>
       </c>
       <c r="J10" s="130" t="n"/>
-      <c r="K10" s="131">
-        <f>F10</f>
-        <v/>
-      </c>
-      <c r="L10" s="131">
-        <f>K10*0.1</f>
-        <v/>
-      </c>
-      <c r="M10" s="131">
-        <f>SUM(K10:L10)</f>
-        <v/>
-      </c>
+      <c r="K10" s="131" t="n"/>
+      <c r="L10" s="131" t="n"/>
+      <c r="M10" s="131" t="n"/>
     </row>
     <row r="11" ht="47.25" customHeight="1">
       <c r="A11" s="123" t="inlineStr">
@@ -15909,10 +14733,7 @@
       <c r="E11" s="126" t="n">
         <v>151000</v>
       </c>
-      <c r="F11" s="127">
-        <f>E11*1.15</f>
-        <v/>
-      </c>
+      <c r="F11" s="127" t="n"/>
       <c r="G11" s="128" t="n">
         <v>0</v>
       </c>
@@ -15925,18 +14746,9 @@
         <v>2339</v>
       </c>
       <c r="J11" s="130" t="n"/>
-      <c r="K11" s="131">
-        <f>F11</f>
-        <v/>
-      </c>
-      <c r="L11" s="131">
-        <f>K11*0.1</f>
-        <v/>
-      </c>
-      <c r="M11" s="131">
-        <f>SUM(K11:L11)</f>
-        <v/>
-      </c>
+      <c r="K11" s="131" t="n"/>
+      <c r="L11" s="131" t="n"/>
+      <c r="M11" s="131" t="n"/>
     </row>
     <row r="12" ht="33.75" customHeight="1">
       <c r="A12" s="123" t="inlineStr">
@@ -15957,14 +14769,8 @@
           <t>Short-Term Non Classified, Non-Instructional</t>
         </is>
       </c>
-      <c r="E12" s="126">
-        <f>88000*B12</f>
-        <v/>
-      </c>
-      <c r="F12" s="127">
-        <f>E12*1.15</f>
-        <v/>
-      </c>
+      <c r="E12" s="126" t="n"/>
+      <c r="F12" s="127" t="n"/>
       <c r="G12" s="128" t="n">
         <v>30000</v>
       </c>
@@ -15977,18 +14783,9 @@
         <v>2339</v>
       </c>
       <c r="J12" s="136" t="n"/>
-      <c r="K12" s="131">
-        <f>F12</f>
-        <v/>
-      </c>
-      <c r="L12" s="131">
-        <f>K12*0.1</f>
-        <v/>
-      </c>
-      <c r="M12" s="131">
-        <f>SUM(K12:L12)</f>
-        <v/>
-      </c>
+      <c r="K12" s="131" t="n"/>
+      <c r="L12" s="131" t="n"/>
+      <c r="M12" s="131" t="n"/>
     </row>
     <row r="13" ht="48.75" customHeight="1">
       <c r="A13" s="123" t="inlineStr">
@@ -16012,10 +14809,7 @@
       <c r="E13" s="126" t="n">
         <v>80000</v>
       </c>
-      <c r="F13" s="127">
-        <f>E13*1.15</f>
-        <v/>
-      </c>
+      <c r="F13" s="127" t="n"/>
       <c r="G13" s="128" t="n">
         <v>15000</v>
       </c>
@@ -16028,18 +14822,9 @@
         <v>2339</v>
       </c>
       <c r="J13" s="130" t="n"/>
-      <c r="K13" s="131">
-        <f>F13</f>
-        <v/>
-      </c>
-      <c r="L13" s="131">
-        <f>K13*0.1</f>
-        <v/>
-      </c>
-      <c r="M13" s="131">
-        <f>SUM(K13:L13)</f>
-        <v/>
-      </c>
+      <c r="K13" s="131" t="n"/>
+      <c r="L13" s="131" t="n"/>
+      <c r="M13" s="131" t="n"/>
     </row>
     <row r="14" ht="48.75" customHeight="1">
       <c r="A14" s="123" t="inlineStr">
@@ -16063,10 +14848,7 @@
       <c r="E14" s="126" t="n">
         <v>88000</v>
       </c>
-      <c r="F14" s="127">
-        <f>E14*1.15</f>
-        <v/>
-      </c>
+      <c r="F14" s="127" t="n"/>
       <c r="G14" s="128" t="n">
         <v>15000</v>
       </c>
@@ -16079,18 +14861,9 @@
         <v>2339</v>
       </c>
       <c r="J14" s="130" t="n"/>
-      <c r="K14" s="131">
-        <f>F14*B14</f>
-        <v/>
-      </c>
-      <c r="L14" s="131">
-        <f>K14*0.1</f>
-        <v/>
-      </c>
-      <c r="M14" s="131">
-        <f>SUM(K14:L14)</f>
-        <v/>
-      </c>
+      <c r="K14" s="131" t="n"/>
+      <c r="L14" s="131" t="n"/>
+      <c r="M14" s="131" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="137" t="inlineStr">
@@ -16098,36 +14871,18 @@
           <t>Total FTE</t>
         </is>
       </c>
-      <c r="B15" s="138">
-        <f>SUM(B2:B13)</f>
-        <v/>
-      </c>
+      <c r="B15" s="138" t="n"/>
       <c r="C15" s="138" t="n"/>
       <c r="D15" s="139" t="n"/>
       <c r="E15" s="140" t="n"/>
-      <c r="F15" s="141">
-        <f>SUM(F2:F13)</f>
-        <v/>
-      </c>
-      <c r="G15" s="141">
-        <f>SUM(G2:G13)</f>
-        <v/>
-      </c>
+      <c r="F15" s="141" t="n"/>
+      <c r="G15" s="141" t="n"/>
       <c r="H15" s="142" t="n"/>
       <c r="I15" s="143" t="n"/>
       <c r="J15" s="144" t="n"/>
-      <c r="K15" s="145">
-        <f>SUM(K2:K13)</f>
-        <v/>
-      </c>
-      <c r="L15" s="145">
-        <f>SUM(L2:L13)</f>
-        <v/>
-      </c>
-      <c r="M15" s="145">
-        <f>SUM(M2:M13)</f>
-        <v/>
-      </c>
+      <c r="K15" s="145" t="n"/>
+      <c r="L15" s="145" t="n"/>
+      <c r="M15" s="145" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="146" t="n"/>
@@ -16436,10 +15191,7 @@
       <c r="E27" s="156" t="n">
         <v>5198</v>
       </c>
-      <c r="F27" s="157">
-        <f>D27+D28+D29</f>
-        <v/>
-      </c>
+      <c r="F27" s="157" t="n"/>
       <c r="G27" s="149" t="n"/>
       <c r="H27" s="150" t="n"/>
       <c r="I27" s="150" t="n"/>
@@ -16597,10 +15349,7 @@
         <v>372000</v>
       </c>
       <c r="E33" s="156" t="n"/>
-      <c r="F33" s="161">
-        <f>SUM(F18:F32)</f>
-        <v/>
-      </c>
+      <c r="F33" s="161" t="n"/>
       <c r="G33" s="122" t="n"/>
       <c r="H33" s="150" t="n"/>
       <c r="I33" s="150" t="n"/>
@@ -16637,14 +15386,8 @@
         </is>
       </c>
       <c r="B35" s="155" t="n"/>
-      <c r="C35" s="126">
-        <f>SUM(C18:C34)</f>
-        <v/>
-      </c>
-      <c r="D35" s="162">
-        <f>SUM(D18:D34)</f>
-        <v/>
-      </c>
+      <c r="C35" s="126" t="n"/>
+      <c r="D35" s="162" t="n"/>
       <c r="E35" s="149" t="n"/>
       <c r="F35" s="149" t="n"/>
       <c r="G35" s="149" t="n"/>
@@ -16682,4 +15425,254 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="221" t="inlineStr">
+        <is>
+          <t>Parameter</t>
+        </is>
+      </c>
+      <c r="B1" s="221" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C1" s="221" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D1" s="221" t="inlineStr">
+        <is>
+          <t>Last Modified</t>
+        </is>
+      </c>
+      <c r="E1" s="221" t="inlineStr">
+        <is>
+          <t>Where Applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>SAVINGS_DEFAULT</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>$269M</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Fallback value for Estimated Savings when live scrape unavailable.</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>this file (fallback only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>TIER_MIN_STUDENTS</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>500</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Min CPL students for one tier criterion (college-level).</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>cloudflare-worker-proxy.js L184</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>TIER_MIN_UNITS</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Min CPL eligible units for one tier criterion.</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>cloudflare-worker-proxy.js L185</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>TIER_MIN_AVG_UNITS_PER_STUDENT</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Min average eligible units per student for one tier criterion.</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>cloudflare-worker-proxy.js L186</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>TIER_MIN_TRANSCRIPTION_RATE</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Min TranscribedUnits/Units ratio for one tier criterion (0.25 = 25%).</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>cloudflare-worker-proxy.js L187</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>TIER_MIN_AVG_TRANSCRIBED_PER_STUDENT</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Min average transcribed units per student for one tier criterion.</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>cloudflare-worker-proxy.js L188</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>BEACON_PER_UNIT_SAVINGS</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1420</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Per-unit savings factor (Beacon Economics). CCCCO computes the savings; this value is documentation only.</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>CCCCO dashboard (reference)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>TWENTY_YEAR_MULTIPLIER</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>4</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Multiplier applied by CCCCO to one-year impact for 20-year projection.</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>CCCCO dashboard (reference)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/CPL_Initiative_Project_List_v3.xlsx
+++ b/CPL_Initiative_Project_List_v3.xlsx
@@ -2464,7 +2464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG52"/>
+  <dimension ref="A1:AD52"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="16" defaultRowHeight="15" outlineLevelRow="1"/>
   <cols>
     <col width="6" customWidth="1" style="187" min="1" max="1"/>
@@ -4115,7 +4115,7 @@
       </c>
       <c r="B15" s="171" t="inlineStr">
         <is>
-          <t>CPL Offers &amp; Awards Tracking</t>
+          <t>CPL Offers &amp; Awards Tracking — Apprentice Cohort</t>
         </is>
       </c>
       <c r="C15" s="172" t="inlineStr">

--- a/CPL_Initiative_Project_List_v3.xlsx
+++ b/CPL_Initiative_Project_List_v3.xlsx
@@ -3731,7 +3731,7 @@
       </c>
       <c r="B12" s="171" t="inlineStr">
         <is>
-          <t>CPL Offers &amp; Awards Tracking</t>
+          <t>CPL Offers &amp; Awards Tracking — All Populations</t>
         </is>
       </c>
       <c r="C12" s="172" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="B13" s="171" t="inlineStr">
         <is>
-          <t>CPL Offers &amp; Awards Tracking</t>
+          <t>CPL Offers &amp; Awards Tracking — Working Adults</t>
         </is>
       </c>
       <c r="C13" s="172" t="inlineStr">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="B14" s="171" t="inlineStr">
         <is>
-          <t>CPL Offers &amp; Awards Tracking</t>
+          <t>CPL Offers &amp; Awards Tracking — Veterans &amp; Service Members</t>
         </is>
       </c>
       <c r="C14" s="172" t="inlineStr">
